--- a/R Markdown/resultados/df_ciclo_2022_2025.xlsx
+++ b/R Markdown/resultados/df_ciclo_2022_2025.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -397,12 +397,22 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>idrgp_diferenca_ciclo</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>idrgp_var_pct_ciclo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>status_ciclo</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>status_ciclo_estatistico</t>
         </is>
       </c>
     </row>
@@ -419,7 +429,7 @@
         <v>268083860.93</v>
       </c>
       <c r="D2">
-        <v>645381828.96</v>
+        <v>600441154.33</v>
       </c>
       <c r="E2">
         <v>737074530.21</v>
@@ -428,15 +438,23 @@
         <v>985402150.88</v>
       </c>
       <c r="G2">
-        <v>2635942370.98</v>
+        <v>2591001696.35</v>
       </c>
       <c r="H2">
-        <v>0.01312168036510893</v>
+        <v>0.01706572090368024</v>
       </c>
       <c r="I2">
-        <v>0.02666508203053075</v>
-      </c>
-      <c r="J2" t="inlineStr">
+        <v>0.004284843678210599</v>
+      </c>
+      <c r="J2">
+        <v>0.3352542710974324</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>Dentro do IDRGP Alvo</t>
         </is>
@@ -455,7 +473,7 @@
         <v>529830929.79</v>
       </c>
       <c r="D3">
-        <v>3142625094.65</v>
+        <v>1086938304.9</v>
       </c>
       <c r="E3">
         <v>1370494139.28</v>
@@ -464,15 +482,23 @@
         <v>2112006389.73</v>
       </c>
       <c r="G3">
-        <v>7154956553.450001</v>
+        <v>5099269763.700001</v>
       </c>
       <c r="H3">
-        <v>0.03561726309126684</v>
+        <v>0.03358651394264638</v>
       </c>
       <c r="I3">
-        <v>0.134993310745922</v>
-      </c>
-      <c r="J3" t="inlineStr">
+        <v>0.002205480456326507</v>
+      </c>
+      <c r="J3">
+        <v>0.07028068267056774</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>Dentro do IDRGP Alvo</t>
         </is>
@@ -491,7 +517,7 @@
         <v>1135615346.88</v>
       </c>
       <c r="D4">
-        <v>3723645915.23</v>
+        <v>1893010845.67</v>
       </c>
       <c r="E4">
         <v>1802521652.49</v>
@@ -500,15 +526,23 @@
         <v>2560599212.5</v>
       </c>
       <c r="G4">
-        <v>9222382127.1</v>
+        <v>7391747057.54</v>
       </c>
       <c r="H4">
-        <v>0.04590887562982226</v>
+        <v>0.04868599370362481</v>
       </c>
       <c r="I4">
-        <v>-0.348796295970359</v>
-      </c>
-      <c r="J4" t="inlineStr">
+        <v>-0.02181249293847914</v>
+      </c>
+      <c r="J4">
+        <v>-0.309403704638562</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>Abaixo do IDRGP Alvo</t>
         </is>
@@ -527,7 +561,7 @@
         <v>901971023.1900001</v>
       </c>
       <c r="D5">
-        <v>619219193.39</v>
+        <v>1726163460.9</v>
       </c>
       <c r="E5">
         <v>2114329482</v>
@@ -536,15 +570,23 @@
         <v>3213515525.28</v>
       </c>
       <c r="G5">
-        <v>6849035223.860001</v>
+        <v>7955979491.370001</v>
       </c>
       <c r="H5">
-        <v>0.03409439144280333</v>
+        <v>0.0524023298426986</v>
       </c>
       <c r="I5">
-        <v>-0.585604209789149</v>
-      </c>
-      <c r="J5" t="inlineStr">
+        <v>-0.02987261659306412</v>
+      </c>
+      <c r="J5">
+        <v>-0.363082783850702</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>Abaixo do IDRGP Alvo</t>
         </is>
@@ -563,7 +605,7 @@
         <v>154312005.2</v>
       </c>
       <c r="D6">
-        <v>2853148426.42</v>
+        <v>842834351.62</v>
       </c>
       <c r="E6">
         <v>745939592.83</v>
@@ -572,15 +614,23 @@
         <v>989313791.46</v>
       </c>
       <c r="G6">
-        <v>4742713815.91</v>
+        <v>2732399741.11</v>
       </c>
       <c r="H6">
-        <v>0.02360915604252006</v>
+        <v>0.01799704394048086</v>
       </c>
       <c r="I6">
-        <v>0.03069480617082193</v>
-      </c>
-      <c r="J6" t="inlineStr">
+        <v>-0.004909015060855754</v>
+      </c>
+      <c r="J6">
+        <v>-0.2143107664469607</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>Dentro do IDRGP Alvo</t>
         </is>
@@ -599,7 +649,7 @@
         <v>530860636.58</v>
       </c>
       <c r="D7">
-        <v>529096120.88</v>
+        <v>1031792894.37</v>
       </c>
       <c r="E7">
         <v>1014230423.52</v>
@@ -608,15 +658,23 @@
         <v>1687158182.77</v>
       </c>
       <c r="G7">
-        <v>3761345363.75</v>
+        <v>4264042137.24</v>
       </c>
       <c r="H7">
-        <v>0.01872391906184294</v>
+        <v>0.02808525873919003</v>
       </c>
       <c r="I7">
-        <v>-0.6550246689618459</v>
-      </c>
-      <c r="J7" t="inlineStr">
+        <v>-0.02619085139742748</v>
+      </c>
+      <c r="J7">
+        <v>-0.4825484238185624</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>Abaixo do IDRGP Alvo</t>
         </is>
@@ -635,7 +693,7 @@
         <v>318218981.72</v>
       </c>
       <c r="D8">
-        <v>2236230158.87</v>
+        <v>434812479.76</v>
       </c>
       <c r="E8">
         <v>902673292.38</v>
@@ -644,15 +702,23 @@
         <v>1335237845.73</v>
       </c>
       <c r="G8">
-        <v>4792360278.7</v>
+        <v>2990942599.59</v>
       </c>
       <c r="H8">
-        <v>0.0238562953666421</v>
+        <v>0.01969994528194852</v>
       </c>
       <c r="I8">
-        <v>-0.03668238012400864</v>
-      </c>
-      <c r="J8" t="inlineStr">
+        <v>-0.005064779118829223</v>
+      </c>
+      <c r="J8">
+        <v>-0.2045158684935804</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>Dentro do IDRGP Alvo</t>
         </is>
@@ -671,7 +737,7 @@
         <v>299824744.02</v>
       </c>
       <c r="D9">
-        <v>1959834389.24</v>
+        <v>419672736.3</v>
       </c>
       <c r="E9">
         <v>500741801.08</v>
@@ -680,15 +746,23 @@
         <v>1133248138.6</v>
       </c>
       <c r="G9">
-        <v>3893649072.94</v>
+        <v>2353487420</v>
       </c>
       <c r="H9">
-        <v>0.01938252488047625</v>
+        <v>0.01550132503449238</v>
       </c>
       <c r="I9">
-        <v>0.2388842285570431</v>
-      </c>
-      <c r="J9" t="inlineStr">
+        <v>-0.0001438211653680532</v>
+      </c>
+      <c r="J9">
+        <v>-0.009192701910918298</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>Dentro do IDRGP Alvo</t>
         </is>
@@ -707,7 +781,7 @@
         <v>658113599.2</v>
       </c>
       <c r="D10">
-        <v>18206639640.81</v>
+        <v>843947046.97</v>
       </c>
       <c r="E10">
         <v>1100647553.21</v>
@@ -716,17 +790,25 @@
         <v>2299120389.61</v>
       </c>
       <c r="G10">
-        <v>22264521182.83</v>
+        <v>4901828588.99</v>
       </c>
       <c r="H10">
-        <v>0.1108324421882852</v>
+        <v>0.03228606092200873</v>
       </c>
       <c r="I10">
-        <v>1.466296771969547</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
+        <v>-0.01265274913845942</v>
+      </c>
+      <c r="J10">
+        <v>-0.2815550550055576</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -743,7 +825,7 @@
         <v>516585406.56</v>
       </c>
       <c r="D11">
-        <v>1061808264.89</v>
+        <v>686451804.38</v>
       </c>
       <c r="E11">
         <v>920953728.14</v>
@@ -752,17 +834,25 @@
         <v>1000682748.19</v>
       </c>
       <c r="G11">
-        <v>3500030147.78</v>
+        <v>3124673687.27</v>
       </c>
       <c r="H11">
-        <v>0.01742309595726841</v>
+        <v>0.02058076964486093</v>
       </c>
       <c r="I11">
-        <v>-0.4391135733000383</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
+        <v>-0.01048273114223986</v>
+      </c>
+      <c r="J11">
+        <v>-0.3374613574331211</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -779,7 +869,7 @@
         <v>583297851.04</v>
       </c>
       <c r="D12">
-        <v>5387841714.57</v>
+        <v>1081771738.47</v>
       </c>
       <c r="E12">
         <v>1187638555.17</v>
@@ -788,17 +878,25 @@
         <v>1586731172.63</v>
       </c>
       <c r="G12">
-        <v>8745509293.41</v>
+        <v>4439439317.31</v>
       </c>
       <c r="H12">
-        <v>0.04353501003724576</v>
+        <v>0.02924051823847321</v>
       </c>
       <c r="I12">
-        <v>0.5260782128683421</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
+        <v>0.0007131402376959924</v>
+      </c>
+      <c r="J12">
+        <v>0.02499845017921251</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -815,7 +913,7 @@
         <v>677605266.5599999</v>
       </c>
       <c r="D13">
-        <v>1566424290.79</v>
+        <v>729781207.34</v>
       </c>
       <c r="E13">
         <v>809483850.37</v>
@@ -824,15 +922,23 @@
         <v>1202045954.4</v>
       </c>
       <c r="G13">
-        <v>4255559362.12</v>
+        <v>3418916278.67</v>
       </c>
       <c r="H13">
-        <v>0.02118410870406285</v>
+        <v>0.02251880849287939</v>
       </c>
       <c r="I13">
-        <v>-0.3841937914939507</v>
-      </c>
-      <c r="J13" t="inlineStr">
+        <v>-0.01188180067839816</v>
+      </c>
+      <c r="J13">
+        <v>-0.3453950660943165</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>Abaixo do IDRGP Alvo</t>
         </is>
@@ -851,7 +957,7 @@
         <v>880773966.36</v>
       </c>
       <c r="D14">
-        <v>1921365350.61</v>
+        <v>1104357795.92</v>
       </c>
       <c r="E14">
         <v>1381059096.62</v>
@@ -860,15 +966,23 @@
         <v>2038715032.19</v>
       </c>
       <c r="G14">
-        <v>6221913445.78</v>
+        <v>5404905891.09</v>
       </c>
       <c r="H14">
-        <v>0.03097258892824184</v>
+        <v>0.03559959670344393</v>
       </c>
       <c r="I14">
-        <v>-0.3783190028542728</v>
-      </c>
-      <c r="J14" t="inlineStr">
+        <v>-0.01422111370984477</v>
+      </c>
+      <c r="J14">
+        <v>-0.2854458234712681</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>Abaixo do IDRGP Alvo</t>
         </is>
@@ -887,7 +1001,7 @@
         <v>288635829.29</v>
       </c>
       <c r="D15">
-        <v>1352520777.87</v>
+        <v>1149596326.06</v>
       </c>
       <c r="E15">
         <v>1278748563.6</v>
@@ -896,15 +1010,23 @@
         <v>1532409954.11</v>
       </c>
       <c r="G15">
-        <v>4452315124.87</v>
+        <v>4249390673.059999</v>
       </c>
       <c r="H15">
-        <v>0.02216355584874335</v>
+        <v>0.02798875637144617</v>
       </c>
       <c r="I15">
-        <v>0.5136913252442386</v>
-      </c>
-      <c r="J15" t="inlineStr">
+        <v>0.01334669858917857</v>
+      </c>
+      <c r="J15">
+        <v>0.9115316158185236</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>Acima do IDRGP Alvo</t>
         </is>
@@ -923,7 +1045,7 @@
         <v>417194492.06</v>
       </c>
       <c r="D16">
-        <v>1288212197.47</v>
+        <v>716643418.8</v>
       </c>
       <c r="E16">
         <v>1018298108.3</v>
@@ -932,15 +1054,23 @@
         <v>1078973096.78</v>
       </c>
       <c r="G16">
-        <v>3802677894.61</v>
+        <v>3231109115.94</v>
       </c>
       <c r="H16">
-        <v>0.01892967176136963</v>
+        <v>0.02128181022021238</v>
       </c>
       <c r="I16">
-        <v>-0.4770214587913907</v>
-      </c>
-      <c r="J16" t="inlineStr">
+        <v>-0.01491407597737986</v>
+      </c>
+      <c r="J16">
+        <v>-0.412037873474471</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>Abaixo do IDRGP Alvo</t>
         </is>
@@ -959,7 +1089,7 @@
         <v>438963711.58</v>
       </c>
       <c r="D17">
-        <v>701778701.86</v>
+        <v>1105161010.6</v>
       </c>
       <c r="E17">
         <v>1270053924.95</v>
@@ -968,15 +1098,23 @@
         <v>1621677779.68</v>
       </c>
       <c r="G17">
-        <v>4032474118.070001</v>
+        <v>4435856426.81</v>
       </c>
       <c r="H17">
-        <v>0.02007359380858428</v>
+        <v>0.02921691940818778</v>
       </c>
       <c r="I17">
-        <v>0.6773290308981015</v>
-      </c>
-      <c r="J17" t="inlineStr">
+        <v>0.01724932483442895</v>
+      </c>
+      <c r="J17">
+        <v>1.441335995142356</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>Acima do IDRGP Alvo</t>
         </is>
@@ -995,7 +1133,7 @@
         <v>407347161.41</v>
       </c>
       <c r="D18">
-        <v>2349259805.2</v>
+        <v>1414739277.9</v>
       </c>
       <c r="E18">
         <v>1550313121.75</v>
@@ -1004,15 +1142,23 @@
         <v>3031872611.37</v>
       </c>
       <c r="G18">
-        <v>7338792699.73</v>
+        <v>6404272172.43</v>
       </c>
       <c r="H18">
-        <v>0.03653239658492616</v>
+        <v>0.04218195674663604</v>
       </c>
       <c r="I18">
-        <v>-0.5243183725492275</v>
-      </c>
-      <c r="J18" t="inlineStr">
+        <v>-0.03461814331337066</v>
+      </c>
+      <c r="J18">
+        <v>-0.450756487118145</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>Abaixo do IDRGP Alvo</t>
         </is>
@@ -1031,7 +1177,7 @@
         <v>443362279.2</v>
       </c>
       <c r="D19">
-        <v>1205629513.93</v>
+        <v>1177863319.16</v>
       </c>
       <c r="E19">
         <v>1879548379.37</v>
@@ -1040,15 +1186,23 @@
         <v>2415683562.03</v>
       </c>
       <c r="G19">
-        <v>5944223734.530001</v>
+        <v>5916457539.76</v>
       </c>
       <c r="H19">
-        <v>0.0295902538393502</v>
+        <v>0.03896894905713704</v>
       </c>
       <c r="I19">
-        <v>0.9484024463815081</v>
-      </c>
-      <c r="J19" t="inlineStr">
+        <v>0.02378201788985998</v>
+      </c>
+      <c r="J19">
+        <v>1.565952833255909</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>Acima do IDRGP Alvo</t>
         </is>
@@ -1067,7 +1221,7 @@
         <v>254026720.87</v>
       </c>
       <c r="D20">
-        <v>1106053510.28</v>
+        <v>599141447.25</v>
       </c>
       <c r="E20">
         <v>891442908.4</v>
@@ -1076,15 +1230,23 @@
         <v>1292475939.08</v>
       </c>
       <c r="G20">
-        <v>3543999078.63</v>
+        <v>3037087015.6</v>
       </c>
       <c r="H20">
-        <v>0.01764197261518061</v>
+        <v>0.02000387704934154</v>
       </c>
       <c r="I20">
-        <v>-0.5787560330645473</v>
-      </c>
-      <c r="J20" t="inlineStr">
+        <v>-0.02187677644351642</v>
+      </c>
+      <c r="J20">
+        <v>-0.5223599590499975</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>Abaixo do IDRGP Alvo</t>
         </is>
@@ -1103,7 +1265,7 @@
         <v>409432833.7</v>
       </c>
       <c r="D21">
-        <v>3335881874.71</v>
+        <v>1002662305.98</v>
       </c>
       <c r="E21">
         <v>1355941790.68</v>
@@ -1112,15 +1274,23 @@
         <v>1702354442.56</v>
       </c>
       <c r="G21">
-        <v>6803610941.65</v>
+        <v>4470391372.92</v>
       </c>
       <c r="H21">
-        <v>0.03386827006832406</v>
+        <v>0.02944438500675035</v>
       </c>
       <c r="I21">
-        <v>0.01747246007408348</v>
-      </c>
-      <c r="J21" t="inlineStr">
+        <v>-0.003842285048042161</v>
+      </c>
+      <c r="J21">
+        <v>-0.1154301419071795</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>Dentro do IDRGP Alvo</t>
         </is>
@@ -1139,7 +1309,7 @@
         <v>317894841.59</v>
       </c>
       <c r="D22">
-        <v>1614967083.44</v>
+        <v>378277168.48</v>
       </c>
       <c r="E22">
         <v>643891246.63</v>
@@ -1148,15 +1318,23 @@
         <v>915880639.14</v>
       </c>
       <c r="G22">
-        <v>3492633810.8</v>
+        <v>2255943895.84</v>
       </c>
       <c r="H22">
-        <v>0.01738627710614606</v>
+        <v>0.01485885129098963</v>
       </c>
       <c r="I22">
-        <v>-0.1844777785260587</v>
-      </c>
-      <c r="J22" t="inlineStr">
+        <v>-0.006460343512461365</v>
+      </c>
+      <c r="J22">
+        <v>-0.3030294329603673</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>Dentro do IDRGP Alvo</t>
         </is>
@@ -1175,7 +1353,7 @@
         <v>176159856.34</v>
       </c>
       <c r="D23">
-        <v>1018668371.93</v>
+        <v>681661685.0599999</v>
       </c>
       <c r="E23">
         <v>623666594.01</v>
@@ -1184,17 +1362,25 @@
         <v>996106805.3</v>
       </c>
       <c r="G23">
-        <v>2814601627.58</v>
+        <v>2477594940.71</v>
       </c>
       <c r="H23">
-        <v>0.01401104338198764</v>
+        <v>0.0163187634458482</v>
       </c>
       <c r="I23">
-        <v>1.221728236454763</v>
-      </c>
-      <c r="J23" t="inlineStr">
+        <v>0.0100123920579843</v>
+      </c>
+      <c r="J23">
+        <v>1.587662927250421</v>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1397,7 @@
         <v>367540618.45</v>
       </c>
       <c r="D24">
-        <v>779908407.73</v>
+        <v>624679391.73</v>
       </c>
       <c r="E24">
         <v>856333446.46</v>
@@ -1220,15 +1406,23 @@
         <v>1780968666.97</v>
       </c>
       <c r="G24">
-        <v>3784751139.61</v>
+        <v>3629522123.61</v>
       </c>
       <c r="H24">
-        <v>0.0188404326521678</v>
+        <v>0.02390597106227984</v>
       </c>
       <c r="I24">
-        <v>-0.4694327980787169</v>
-      </c>
-      <c r="J24" t="inlineStr">
+        <v>-0.01160401256268429</v>
+      </c>
+      <c r="J24">
+        <v>-0.3267816928681001</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>Abaixo do IDRGP Alvo</t>
         </is>
@@ -1247,7 +1441,7 @@
         <v>165422674.2</v>
       </c>
       <c r="D25">
-        <v>1152699551.01</v>
+        <v>1743044894.91</v>
       </c>
       <c r="E25">
         <v>1554935421.67</v>
@@ -1256,15 +1450,23 @@
         <v>1366325941.16</v>
       </c>
       <c r="G25">
-        <v>4239383588.04</v>
+        <v>4829728931.940001</v>
       </c>
       <c r="H25">
-        <v>0.02110358595080666</v>
+        <v>0.03181117407565904</v>
       </c>
       <c r="I25">
-        <v>0.4631285825219409</v>
-      </c>
-      <c r="J25" t="inlineStr">
+        <v>0.01738757098095961</v>
+      </c>
+      <c r="J25">
+        <v>1.205494276762885</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>Acima do IDRGP Alvo</t>
         </is>
@@ -1283,7 +1485,7 @@
         <v>213876408.05</v>
       </c>
       <c r="D26">
-        <v>1213834991.17</v>
+        <v>790575300.34</v>
       </c>
       <c r="E26">
         <v>849590055.38</v>
@@ -1292,15 +1494,23 @@
         <v>1660301401.41</v>
       </c>
       <c r="G26">
-        <v>3937602856.01</v>
+        <v>3514343165.18</v>
       </c>
       <c r="H26">
-        <v>0.01960132613297383</v>
+        <v>0.02314734093042313</v>
       </c>
       <c r="I26">
-        <v>1.510278436094193</v>
-      </c>
-      <c r="J26" t="inlineStr">
+        <v>0.01533891384475209</v>
+      </c>
+      <c r="J26">
+        <v>1.964405081389563</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>Acima do IDRGP Alvo</t>
         </is>
@@ -1319,7 +1529,7 @@
         <v>297747200.45</v>
       </c>
       <c r="D27">
-        <v>6027832203.39</v>
+        <v>746739859.46</v>
       </c>
       <c r="E27">
         <v>730973098.37</v>
@@ -1328,17 +1538,25 @@
         <v>1077859469.28</v>
       </c>
       <c r="G27">
-        <v>8134411971.49</v>
+        <v>2853319627.56</v>
       </c>
       <c r="H27">
-        <v>0.04049297701767442</v>
+        <v>0.01879348689023556</v>
       </c>
       <c r="I27">
-        <v>0.418776073291674</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
+        <v>-0.009747293984175068</v>
+      </c>
+      <c r="J27">
+        <v>-0.3415216292457643</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1573,7 @@
         <v>607742680.01</v>
       </c>
       <c r="D28">
-        <v>1762950824.2</v>
+        <v>1096779160.03</v>
       </c>
       <c r="E28">
         <v>1424727936.6</v>
@@ -1364,15 +1582,23 @@
         <v>1955065802.96</v>
       </c>
       <c r="G28">
-        <v>5750487243.77</v>
+        <v>5084315579.6</v>
       </c>
       <c r="H28">
-        <v>0.02862583658395114</v>
+        <v>0.033488017699841</v>
       </c>
       <c r="I28">
-        <v>-0.5044183938101175</v>
-      </c>
-      <c r="J28" t="inlineStr">
+        <v>-0.02427408691907645</v>
+      </c>
+      <c r="J28">
+        <v>-0.420242425015908</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>Abaixo do IDRGP Alvo</t>
         </is>
@@ -1391,7 +1617,7 @@
         <v>451930234.72</v>
       </c>
       <c r="D29">
-        <v>1119844037.89</v>
+        <v>646056157.14</v>
       </c>
       <c r="E29">
         <v>757654983.4</v>
@@ -1400,15 +1626,23 @@
         <v>1356017191.47</v>
       </c>
       <c r="G29">
-        <v>3685446447.48</v>
+        <v>3211658566.73</v>
       </c>
       <c r="H29">
-        <v>0.01834609543021975</v>
+        <v>0.02115369851549649</v>
       </c>
       <c r="I29">
-        <v>-0.5410808850590568</v>
-      </c>
-      <c r="J29" t="inlineStr">
+        <v>-0.01882305301419442</v>
+      </c>
+      <c r="J29">
+        <v>-0.4708499889045375</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>Abaixo do IDRGP Alvo</t>
         </is>
@@ -1427,7 +1661,7 @@
         <v>2362273524.69</v>
       </c>
       <c r="D30">
-        <v>5900795535.01</v>
+        <v>4671432106.78</v>
       </c>
       <c r="E30">
         <v>11259293445.76</v>
@@ -1436,15 +1670,23 @@
         <v>6783905505.23</v>
       </c>
       <c r="G30">
-        <v>26306268010.69</v>
+        <v>25076904582.46</v>
       </c>
       <c r="H30">
-        <v>0.130952195402827</v>
+        <v>0.1651698859693348</v>
       </c>
       <c r="I30">
-        <v>6.37950172420026</v>
-      </c>
-      <c r="J30" t="inlineStr">
+        <v>0.1474244879333964</v>
+      </c>
+      <c r="J30">
+        <v>8.307758869923862</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>Acima do IDRGP Alvo</t>
         </is>
@@ -1463,7 +1705,7 @@
         <v>310130761.22</v>
       </c>
       <c r="D31">
-        <v>856223388.3200001</v>
+        <v>885501416.5700001</v>
       </c>
       <c r="E31">
         <v>1250274401.01</v>
@@ -1472,15 +1714,23 @@
         <v>1589744832.47</v>
       </c>
       <c r="G31">
-        <v>4006373383.02</v>
+        <v>4035651411.27</v>
       </c>
       <c r="H31">
-        <v>0.01994366475308176</v>
+        <v>0.02658095544526181</v>
       </c>
       <c r="I31">
-        <v>0.3554307232295518</v>
-      </c>
-      <c r="J31" t="inlineStr">
+        <v>0.01186706087928762</v>
+      </c>
+      <c r="J31">
+        <v>0.8065207227140357</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>Acima do IDRGP Alvo</t>
         </is>
@@ -1499,7 +1749,7 @@
         <v>268759034.4</v>
       </c>
       <c r="D32">
-        <v>1981409700.4</v>
+        <v>918101079.46</v>
       </c>
       <c r="E32">
         <v>1373080195.35</v>
@@ -1508,15 +1758,23 @@
         <v>1934281944.28</v>
       </c>
       <c r="G32">
-        <v>5557530874.43</v>
+        <v>4494222253.49</v>
       </c>
       <c r="H32">
-        <v>0.02766530276091841</v>
+        <v>0.0296013479131311</v>
       </c>
       <c r="I32">
-        <v>2.480118068573606</v>
-      </c>
-      <c r="J32" t="inlineStr">
+        <v>0.02165181797886149</v>
+      </c>
+      <c r="J32">
+        <v>2.723660160775384</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>Acima do IDRGP Alvo</t>
         </is>
@@ -1535,7 +1793,7 @@
         <v>190668608.27</v>
       </c>
       <c r="D33">
-        <v>3759086816.6</v>
+        <v>490592596.61</v>
       </c>
       <c r="E33">
         <v>490806393.49</v>
@@ -1544,17 +1802,25 @@
         <v>776448481.35</v>
       </c>
       <c r="G33">
-        <v>5217010299.71</v>
+        <v>1948516079.72</v>
       </c>
       <c r="H33">
-        <v>0.02597019660518033</v>
+        <v>0.01283396751136005</v>
       </c>
       <c r="I33">
-        <v>0.7659982511817655</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
+        <v>-0.001871707643075505</v>
+      </c>
+      <c r="J33">
+        <v>-0.1272779130110838</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
         </is>
       </c>
     </row>

--- a/R Markdown/resultados/df_ciclo_2022_2025.xlsx
+++ b/R Markdown/resultados/df_ciclo_2022_2025.xlsx
@@ -426,7 +426,7 @@
         <v>0.01278087722546964</v>
       </c>
       <c r="C2">
-        <v>268083860.93</v>
+        <v>270800600.28</v>
       </c>
       <c r="D2">
         <v>600441154.33</v>
@@ -435,19 +435,19 @@
         <v>737074530.21</v>
       </c>
       <c r="F2">
-        <v>985402150.88</v>
+        <v>989484961.0599999</v>
       </c>
       <c r="G2">
-        <v>2591001696.35</v>
+        <v>2597801245.88</v>
       </c>
       <c r="H2">
-        <v>0.01706572090368024</v>
+        <v>0.01706066772054106</v>
       </c>
       <c r="I2">
-        <v>0.004284843678210599</v>
+        <v>0.004279790495071413</v>
       </c>
       <c r="J2">
-        <v>0.3352542710974324</v>
+        <v>0.3348589004941442</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -470,7 +470,7 @@
         <v>0.03138103348631988</v>
       </c>
       <c r="C3">
-        <v>529830929.79</v>
+        <v>531726447.48</v>
       </c>
       <c r="D3">
         <v>1086938304.9</v>
@@ -479,19 +479,19 @@
         <v>1370494139.28</v>
       </c>
       <c r="F3">
-        <v>2112006389.73</v>
+        <v>2120033849.32</v>
       </c>
       <c r="G3">
-        <v>5099269763.700001</v>
+        <v>5109192740.98</v>
       </c>
       <c r="H3">
-        <v>0.03358651394264638</v>
+        <v>0.03355385244052139</v>
       </c>
       <c r="I3">
-        <v>0.002205480456326507</v>
+        <v>0.002172818954201516</v>
       </c>
       <c r="J3">
-        <v>0.07028068267056774</v>
+        <v>0.06923987876781452</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         <v>0.07049848664210395</v>
       </c>
       <c r="C4">
-        <v>1135615346.88</v>
+        <v>1136043087.37</v>
       </c>
       <c r="D4">
         <v>1893010845.67</v>
@@ -523,19 +523,19 @@
         <v>1802521652.49</v>
       </c>
       <c r="F4">
-        <v>2560599212.5</v>
+        <v>2562583888.81</v>
       </c>
       <c r="G4">
-        <v>7391747057.54</v>
+        <v>7394159474.34</v>
       </c>
       <c r="H4">
-        <v>0.04868599370362481</v>
+        <v>0.04856002670122379</v>
       </c>
       <c r="I4">
-        <v>-0.02181249293847914</v>
+        <v>-0.02193845994088016</v>
       </c>
       <c r="J4">
-        <v>-0.309403704638562</v>
+        <v>-0.311190508985732</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -558,7 +558,7 @@
         <v>0.08227494643576272</v>
       </c>
       <c r="C5">
-        <v>901971023.1900001</v>
+        <v>903229166.3</v>
       </c>
       <c r="D5">
         <v>1726163460.9</v>
@@ -567,19 +567,19 @@
         <v>2114329482</v>
       </c>
       <c r="F5">
-        <v>3213515525.28</v>
+        <v>3217471932.62</v>
       </c>
       <c r="G5">
-        <v>7955979491.370001</v>
+        <v>7961194041.82</v>
       </c>
       <c r="H5">
-        <v>0.0524023298426986</v>
+        <v>0.05228394066776743</v>
       </c>
       <c r="I5">
-        <v>-0.02987261659306412</v>
+        <v>-0.02999100576799529</v>
       </c>
       <c r="J5">
-        <v>-0.363082783850702</v>
+        <v>-0.3645217294843354</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         <v>0.02290605900133662</v>
       </c>
       <c r="C6">
-        <v>154312005.2</v>
+        <v>156688314.62</v>
       </c>
       <c r="D6">
         <v>842834351.62</v>
@@ -611,19 +611,19 @@
         <v>745939592.83</v>
       </c>
       <c r="F6">
-        <v>989313791.46</v>
+        <v>990146048.22</v>
       </c>
       <c r="G6">
-        <v>2732399741.11</v>
+        <v>2735608307.29</v>
       </c>
       <c r="H6">
-        <v>0.01799704394048086</v>
+        <v>0.01796569480372878</v>
       </c>
       <c r="I6">
-        <v>-0.004909015060855754</v>
+        <v>-0.004940364197607842</v>
       </c>
       <c r="J6">
-        <v>-0.2143107664469607</v>
+        <v>-0.2156793622735173</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
         <v>0.05427611013661751</v>
       </c>
       <c r="C7">
-        <v>530860636.58</v>
+        <v>530941174.36</v>
       </c>
       <c r="D7">
         <v>1031792894.37</v>
@@ -655,19 +655,19 @@
         <v>1014230423.52</v>
       </c>
       <c r="F7">
-        <v>1687158182.77</v>
+        <v>1688434491</v>
       </c>
       <c r="G7">
-        <v>4264042137.24</v>
+        <v>4265398983.25</v>
       </c>
       <c r="H7">
-        <v>0.02808525873919003</v>
+        <v>0.02801236425002599</v>
       </c>
       <c r="I7">
-        <v>-0.02619085139742748</v>
+        <v>-0.02626374588659152</v>
       </c>
       <c r="J7">
-        <v>-0.4825484238185624</v>
+        <v>-0.4838914546470532</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>0.02476472440077774</v>
       </c>
       <c r="C8">
-        <v>318218981.72</v>
+        <v>323404422.56</v>
       </c>
       <c r="D8">
         <v>434812479.76</v>
@@ -702,16 +702,16 @@
         <v>1335237845.73</v>
       </c>
       <c r="G8">
-        <v>2990942599.59</v>
+        <v>2996128040.43</v>
       </c>
       <c r="H8">
-        <v>0.01969994528194852</v>
+        <v>0.01967661884335443</v>
       </c>
       <c r="I8">
-        <v>-0.005064779118829223</v>
+        <v>-0.005088105557423311</v>
       </c>
       <c r="J8">
-        <v>-0.2045158684935804</v>
+        <v>-0.2054577904878085</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>0.01564514619986043</v>
       </c>
       <c r="C9">
-        <v>299824744.02</v>
+        <v>300184054.28</v>
       </c>
       <c r="D9">
         <v>419672736.3</v>
@@ -743,19 +743,19 @@
         <v>500741801.08</v>
       </c>
       <c r="F9">
-        <v>1133248138.6</v>
+        <v>1144062973.34</v>
       </c>
       <c r="G9">
-        <v>2353487420</v>
+        <v>2364661565</v>
       </c>
       <c r="H9">
-        <v>0.01550132503449238</v>
+        <v>0.01552955804297244</v>
       </c>
       <c r="I9">
-        <v>-0.0001438211653680532</v>
+        <v>-0.0001155881568879885</v>
       </c>
       <c r="J9">
-        <v>-0.009192701910918298</v>
+        <v>-0.007388116123134705</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>0.04493881006046815</v>
       </c>
       <c r="C10">
-        <v>658113599.2</v>
+        <v>662096967.22</v>
       </c>
       <c r="D10">
         <v>843947046.97</v>
@@ -787,19 +787,19 @@
         <v>1100647553.21</v>
       </c>
       <c r="F10">
-        <v>2299120389.61</v>
+        <v>2301085241.03</v>
       </c>
       <c r="G10">
-        <v>4901828588.99</v>
+        <v>4907776808.43</v>
       </c>
       <c r="H10">
-        <v>0.03228606092200873</v>
+        <v>0.03223108369356346</v>
       </c>
       <c r="I10">
-        <v>-0.01265274913845942</v>
+        <v>-0.01270772636690469</v>
       </c>
       <c r="J10">
-        <v>-0.2815550550055576</v>
+        <v>-0.2827784347161307</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>0.03106350078710079</v>
       </c>
       <c r="C11">
-        <v>516585406.56</v>
+        <v>515288534.05</v>
       </c>
       <c r="D11">
         <v>686451804.38</v>
@@ -831,19 +831,19 @@
         <v>920953728.14</v>
       </c>
       <c r="F11">
-        <v>1000682748.19</v>
+        <v>1001849833.82</v>
       </c>
       <c r="G11">
-        <v>3124673687.27</v>
+        <v>3124543900.39</v>
       </c>
       <c r="H11">
-        <v>0.02058076964486093</v>
+        <v>0.02051997062798372</v>
       </c>
       <c r="I11">
-        <v>-0.01048273114223986</v>
+        <v>-0.01054353015911707</v>
       </c>
       <c r="J11">
-        <v>-0.3374613574331211</v>
+        <v>-0.3394186067880443</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>0.02852737800077722</v>
       </c>
       <c r="C12">
-        <v>583297851.04</v>
+        <v>585362030.52</v>
       </c>
       <c r="D12">
         <v>1081771738.47</v>
@@ -875,19 +875,19 @@
         <v>1187638555.17</v>
       </c>
       <c r="F12">
-        <v>1586731172.63</v>
+        <v>1586731737.63</v>
       </c>
       <c r="G12">
-        <v>4439439317.31</v>
+        <v>4441504061.79</v>
       </c>
       <c r="H12">
-        <v>0.02924051823847321</v>
+        <v>0.02916890778222873</v>
       </c>
       <c r="I12">
-        <v>0.0007131402376959924</v>
+        <v>0.0006415297814515129</v>
       </c>
       <c r="J12">
-        <v>0.02499845017921251</v>
+        <v>0.022488214003896</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>0.03440060917127755</v>
       </c>
       <c r="C13">
-        <v>677605266.5599999</v>
+        <v>677606342.2</v>
       </c>
       <c r="D13">
         <v>729781207.34</v>
@@ -919,19 +919,19 @@
         <v>809483850.37</v>
       </c>
       <c r="F13">
-        <v>1202045954.4</v>
+        <v>1202924802.61</v>
       </c>
       <c r="G13">
-        <v>3418916278.67</v>
+        <v>3419796202.52</v>
       </c>
       <c r="H13">
-        <v>0.02251880849287939</v>
+        <v>0.02245899557392733</v>
       </c>
       <c r="I13">
-        <v>-0.01188180067839816</v>
+        <v>-0.01194161359735021</v>
       </c>
       <c r="J13">
-        <v>-0.3453950660943165</v>
+        <v>-0.347133782948261</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>0.04982071041328871</v>
       </c>
       <c r="C14">
-        <v>880773966.36</v>
+        <v>892661593.1899999</v>
       </c>
       <c r="D14">
         <v>1104357795.92</v>
@@ -963,19 +963,19 @@
         <v>1381059096.62</v>
       </c>
       <c r="F14">
-        <v>2038715032.19</v>
+        <v>2039768606.41</v>
       </c>
       <c r="G14">
-        <v>5404905891.09</v>
+        <v>5417847092.14</v>
       </c>
       <c r="H14">
-        <v>0.03559959670344393</v>
+        <v>0.03558089332133988</v>
       </c>
       <c r="I14">
-        <v>-0.01422111370984477</v>
+        <v>-0.01423981709194883</v>
       </c>
       <c r="J14">
-        <v>-0.2854458234712681</v>
+        <v>-0.2858212372690421</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>0.0146420577822676</v>
       </c>
       <c r="C15">
-        <v>288635829.29</v>
+        <v>289068585.26</v>
       </c>
       <c r="D15">
         <v>1149596326.06</v>
@@ -1007,19 +1007,19 @@
         <v>1278748563.6</v>
       </c>
       <c r="F15">
-        <v>1532409954.11</v>
+        <v>1532982112.9</v>
       </c>
       <c r="G15">
-        <v>4249390673.059999</v>
+        <v>4250395587.82</v>
       </c>
       <c r="H15">
-        <v>0.02798875637144617</v>
+        <v>0.02791383171428368</v>
       </c>
       <c r="I15">
-        <v>0.01334669858917857</v>
+        <v>0.01327177393201608</v>
       </c>
       <c r="J15">
-        <v>0.9115316158185236</v>
+        <v>0.9064145306193908</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>0.03619588619759224</v>
       </c>
       <c r="C16">
-        <v>417194492.06</v>
+        <v>418653600.77</v>
       </c>
       <c r="D16">
         <v>716643418.8</v>
@@ -1054,16 +1054,16 @@
         <v>1078973096.78</v>
       </c>
       <c r="G16">
-        <v>3231109115.94</v>
+        <v>3232568224.65</v>
       </c>
       <c r="H16">
-        <v>0.02128181022021238</v>
+        <v>0.02122940407862152</v>
       </c>
       <c r="I16">
-        <v>-0.01491407597737986</v>
+        <v>-0.01496648211897071</v>
       </c>
       <c r="J16">
-        <v>-0.412037873474471</v>
+        <v>-0.4134857214786549</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>0.01196759457375883</v>
       </c>
       <c r="C17">
-        <v>438963711.58</v>
+        <v>439828459.44</v>
       </c>
       <c r="D17">
         <v>1105161010.6</v>
@@ -1095,19 +1095,19 @@
         <v>1270053924.95</v>
       </c>
       <c r="F17">
-        <v>1621677779.68</v>
+        <v>1635541987.13</v>
       </c>
       <c r="G17">
-        <v>4435856426.81</v>
+        <v>4450585382.12</v>
       </c>
       <c r="H17">
-        <v>0.02921691940818778</v>
+        <v>0.02922854798328708</v>
       </c>
       <c r="I17">
-        <v>0.01724932483442895</v>
+        <v>0.01726095340952825</v>
       </c>
       <c r="J17">
-        <v>1.441335995142356</v>
+        <v>1.442307667020747</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>0.0768001000600067</v>
       </c>
       <c r="C18">
-        <v>407347161.41</v>
+        <v>407603040.74</v>
       </c>
       <c r="D18">
         <v>1414739277.9</v>
@@ -1139,19 +1139,19 @@
         <v>1550313121.75</v>
       </c>
       <c r="F18">
-        <v>3031872611.37</v>
+        <v>3036975936.59</v>
       </c>
       <c r="G18">
-        <v>6404272172.43</v>
+        <v>6409631376.98</v>
       </c>
       <c r="H18">
-        <v>0.04218195674663604</v>
+        <v>0.04209428696950479</v>
       </c>
       <c r="I18">
-        <v>-0.03461814331337066</v>
+        <v>-0.03470581309050191</v>
       </c>
       <c r="J18">
-        <v>-0.450756487118145</v>
+        <v>-0.4518980191872797</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>0.01518693116727706</v>
       </c>
       <c r="C19">
-        <v>443362279.2</v>
+        <v>444011947.82</v>
       </c>
       <c r="D19">
         <v>1177863319.16</v>
@@ -1183,19 +1183,19 @@
         <v>1879548379.37</v>
       </c>
       <c r="F19">
-        <v>2415683562.03</v>
+        <v>2415839399.78</v>
       </c>
       <c r="G19">
-        <v>5916457539.76</v>
+        <v>5917263046.13</v>
       </c>
       <c r="H19">
-        <v>0.03896894905713704</v>
+        <v>0.03886073224622813</v>
       </c>
       <c r="I19">
-        <v>0.02378201788985998</v>
+        <v>0.02367380107895107</v>
       </c>
       <c r="J19">
-        <v>1.565952833255909</v>
+        <v>1.55882717964512</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>0.04188065349285796</v>
       </c>
       <c r="C20">
-        <v>254026720.87</v>
+        <v>254092379.92</v>
       </c>
       <c r="D20">
         <v>599141447.25</v>
@@ -1227,19 +1227,19 @@
         <v>891442908.4</v>
       </c>
       <c r="F20">
-        <v>1292475939.08</v>
+        <v>1294481417.88</v>
       </c>
       <c r="G20">
-        <v>3037087015.6</v>
+        <v>3039158153.45</v>
       </c>
       <c r="H20">
-        <v>0.02000387704934154</v>
+        <v>0.01995921261813833</v>
       </c>
       <c r="I20">
-        <v>-0.02187677644351642</v>
+        <v>-0.02192144087471963</v>
       </c>
       <c r="J20">
-        <v>-0.5223599590499975</v>
+        <v>-0.5234264283497382</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>0.03328667005479251</v>
       </c>
       <c r="C21">
-        <v>409432833.7</v>
+        <v>413735667.28</v>
       </c>
       <c r="D21">
         <v>1002662305.98</v>
@@ -1271,19 +1271,19 @@
         <v>1355941790.68</v>
       </c>
       <c r="F21">
-        <v>1702354442.56</v>
+        <v>1705356170.99</v>
       </c>
       <c r="G21">
-        <v>4470391372.92</v>
+        <v>4477695934.93</v>
       </c>
       <c r="H21">
-        <v>0.02944438500675035</v>
+        <v>0.02940659244836891</v>
       </c>
       <c r="I21">
-        <v>-0.003842285048042161</v>
+        <v>-0.003880077606423601</v>
       </c>
       <c r="J21">
-        <v>-0.1154301419071795</v>
+        <v>-0.1165655080558279</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>0.021319194803451</v>
       </c>
       <c r="C22">
-        <v>317894841.59</v>
+        <v>318856012.44</v>
       </c>
       <c r="D22">
         <v>378277168.48</v>
@@ -1315,19 +1315,19 @@
         <v>643891246.63</v>
       </c>
       <c r="F22">
-        <v>915880639.14</v>
+        <v>918890507.58</v>
       </c>
       <c r="G22">
-        <v>2255943895.84</v>
+        <v>2259914935.13</v>
       </c>
       <c r="H22">
-        <v>0.01485885129098963</v>
+        <v>0.01484165035569546</v>
       </c>
       <c r="I22">
-        <v>-0.006460343512461365</v>
+        <v>-0.006477544447755532</v>
       </c>
       <c r="J22">
-        <v>-0.3030294329603673</v>
+        <v>-0.3038362615227379</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>0.006306371387863901</v>
       </c>
       <c r="C23">
-        <v>176159856.34</v>
+        <v>179126600.35</v>
       </c>
       <c r="D23">
         <v>681661685.0599999</v>
@@ -1359,19 +1359,19 @@
         <v>623666594.01</v>
       </c>
       <c r="F23">
-        <v>996106805.3</v>
+        <v>997429393.05</v>
       </c>
       <c r="G23">
-        <v>2477594940.71</v>
+        <v>2481884272.47</v>
       </c>
       <c r="H23">
-        <v>0.0163187634458482</v>
+        <v>0.01629940048747031</v>
       </c>
       <c r="I23">
-        <v>0.0100123920579843</v>
+        <v>0.009993029099606409</v>
       </c>
       <c r="J23">
-        <v>1.587662927250421</v>
+        <v>1.584592546965626</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>0.03550998362496413</v>
       </c>
       <c r="C24">
-        <v>367540618.45</v>
+        <v>373444861.42</v>
       </c>
       <c r="D24">
         <v>624679391.73</v>
@@ -1403,19 +1403,19 @@
         <v>856333446.46</v>
       </c>
       <c r="F24">
-        <v>1780968666.97</v>
+        <v>1785675753.86</v>
       </c>
       <c r="G24">
-        <v>3629522123.61</v>
+        <v>3640133453.47</v>
       </c>
       <c r="H24">
-        <v>0.02390597106227984</v>
+        <v>0.02390602722458852</v>
       </c>
       <c r="I24">
-        <v>-0.01160401256268429</v>
+        <v>-0.01160395640037561</v>
       </c>
       <c r="J24">
-        <v>-0.3267816928681001</v>
+        <v>-0.3267801112760251</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0.01442360309469943</v>
       </c>
       <c r="C25">
-        <v>165422674.2</v>
+        <v>166699640.05</v>
       </c>
       <c r="D25">
         <v>1743044894.91</v>
@@ -1447,19 +1447,19 @@
         <v>1554935421.67</v>
       </c>
       <c r="F25">
-        <v>1366325941.16</v>
+        <v>1376552981.17</v>
       </c>
       <c r="G25">
-        <v>4829728931.940001</v>
+        <v>4841232937.8</v>
       </c>
       <c r="H25">
-        <v>0.03181117407565904</v>
+        <v>0.03179406686348163</v>
       </c>
       <c r="I25">
-        <v>0.01738757098095961</v>
+        <v>0.0173704637687822</v>
       </c>
       <c r="J25">
-        <v>1.205494276762885</v>
+        <v>1.204308219987398</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>0.00780842708567104</v>
       </c>
       <c r="C26">
-        <v>213876408.05</v>
+        <v>214276208.71</v>
       </c>
       <c r="D26">
         <v>790575300.34</v>
@@ -1491,19 +1491,19 @@
         <v>849590055.38</v>
       </c>
       <c r="F26">
-        <v>1660301401.41</v>
+        <v>1665436605.22</v>
       </c>
       <c r="G26">
-        <v>3514343165.18</v>
+        <v>3519878169.65</v>
       </c>
       <c r="H26">
-        <v>0.02314734093042313</v>
+        <v>0.0231162687924736</v>
       </c>
       <c r="I26">
-        <v>0.01533891384475209</v>
+        <v>0.01530784170680256</v>
       </c>
       <c r="J26">
-        <v>1.964405081389563</v>
+        <v>1.960425773187205</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>0.02854078087441063</v>
       </c>
       <c r="C27">
-        <v>297747200.45</v>
+        <v>297798794.47</v>
       </c>
       <c r="D27">
         <v>746739859.46</v>
@@ -1535,19 +1535,19 @@
         <v>730973098.37</v>
       </c>
       <c r="F27">
-        <v>1077859469.28</v>
+        <v>1078636355.45</v>
       </c>
       <c r="G27">
-        <v>2853319627.56</v>
+        <v>2854148107.75</v>
       </c>
       <c r="H27">
-        <v>0.01879348689023556</v>
+        <v>0.01874418705771267</v>
       </c>
       <c r="I27">
-        <v>-0.009747293984175068</v>
+        <v>-0.009796593816697955</v>
       </c>
       <c r="J27">
-        <v>-0.3415216292457643</v>
+        <v>-0.3432489762563393</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>0.05776210461891745</v>
       </c>
       <c r="C28">
-        <v>607742680.01</v>
+        <v>609449214.6</v>
       </c>
       <c r="D28">
         <v>1096779160.03</v>
@@ -1579,19 +1579,19 @@
         <v>1424727936.6</v>
       </c>
       <c r="F28">
-        <v>1955065802.96</v>
+        <v>1956937590.38</v>
       </c>
       <c r="G28">
-        <v>5084315579.6</v>
+        <v>5087893901.610001</v>
       </c>
       <c r="H28">
-        <v>0.033488017699841</v>
+        <v>0.0334139755265731</v>
       </c>
       <c r="I28">
-        <v>-0.02427408691907645</v>
+        <v>-0.02434812909234436</v>
       </c>
       <c r="J28">
-        <v>-0.420242425015908</v>
+        <v>-0.4215242718903665</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>0.03997675152969091</v>
       </c>
       <c r="C29">
-        <v>451930234.72</v>
+        <v>451987454.6</v>
       </c>
       <c r="D29">
         <v>646056157.14</v>
@@ -1623,19 +1623,19 @@
         <v>757654983.4</v>
       </c>
       <c r="F29">
-        <v>1356017191.47</v>
+        <v>1362970185.21</v>
       </c>
       <c r="G29">
-        <v>3211658566.73</v>
+        <v>3218668780.35</v>
       </c>
       <c r="H29">
-        <v>0.02115369851549649</v>
+        <v>0.02113812157535899</v>
       </c>
       <c r="I29">
-        <v>-0.01882305301419442</v>
+        <v>-0.01883862995433193</v>
       </c>
       <c r="J29">
-        <v>-0.4708499889045375</v>
+        <v>-0.4712396388771206</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1658,28 +1658,28 @@
         <v>0.01774539803593836</v>
       </c>
       <c r="C30">
-        <v>2362273524.69</v>
+        <v>2593261890.04</v>
       </c>
       <c r="D30">
-        <v>4671432106.78</v>
+        <v>4671432106.8</v>
       </c>
       <c r="E30">
         <v>11259293445.76</v>
       </c>
       <c r="F30">
-        <v>6783905505.23</v>
+        <v>6837566518.55</v>
       </c>
       <c r="G30">
-        <v>25076904582.46</v>
+        <v>25361553961.15</v>
       </c>
       <c r="H30">
-        <v>0.1651698859693348</v>
+        <v>0.1665581790346631</v>
       </c>
       <c r="I30">
-        <v>0.1474244879333964</v>
+        <v>0.1488127809987247</v>
       </c>
       <c r="J30">
-        <v>8.307758869923862</v>
+        <v>8.385992847122722</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>0.01471389456597418</v>
       </c>
       <c r="C31">
-        <v>310130761.22</v>
+        <v>310244568.84</v>
       </c>
       <c r="D31">
         <v>885501416.5700001</v>
@@ -1711,19 +1711,19 @@
         <v>1250274401.01</v>
       </c>
       <c r="F31">
-        <v>1589744832.47</v>
+        <v>1594437761.49</v>
       </c>
       <c r="G31">
-        <v>4035651411.27</v>
+        <v>4040458147.91</v>
       </c>
       <c r="H31">
-        <v>0.02658095544526181</v>
+        <v>0.02653509925348209</v>
       </c>
       <c r="I31">
-        <v>0.01186706087928762</v>
+        <v>0.0118212046875079</v>
       </c>
       <c r="J31">
-        <v>0.8065207227140357</v>
+        <v>0.8034041996497913</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>0.007949529934269608</v>
       </c>
       <c r="C32">
-        <v>268759034.4</v>
+        <v>270403481.87</v>
       </c>
       <c r="D32">
         <v>918101079.46</v>
@@ -1755,19 +1755,19 @@
         <v>1373080195.35</v>
       </c>
       <c r="F32">
-        <v>1934281944.28</v>
+        <v>1939351672.66</v>
       </c>
       <c r="G32">
-        <v>4494222253.49</v>
+        <v>4500936429.34</v>
       </c>
       <c r="H32">
-        <v>0.0296013479131311</v>
+        <v>0.02955922088883137</v>
       </c>
       <c r="I32">
-        <v>0.02165181797886149</v>
+        <v>0.02160969095456176</v>
       </c>
       <c r="J32">
-        <v>2.723660160775384</v>
+        <v>2.718360850671761</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>0.01470567515443555</v>
       </c>
       <c r="C33">
-        <v>190668608.27</v>
+        <v>190978482.88</v>
       </c>
       <c r="D33">
         <v>490592596.61</v>
@@ -1802,16 +1802,16 @@
         <v>776448481.35</v>
       </c>
       <c r="G33">
-        <v>1948516079.72</v>
+        <v>1948825954.33</v>
       </c>
       <c r="H33">
-        <v>0.01283396751136005</v>
+        <v>0.01279862041205837</v>
       </c>
       <c r="I33">
-        <v>-0.001871707643075505</v>
+        <v>-0.001907054742377181</v>
       </c>
       <c r="J33">
-        <v>-0.1272779130110838</v>
+        <v>-0.129681549629632</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>

--- a/R Markdown/resultados/df_ciclo_2022_2025.xlsx
+++ b/R Markdown/resultados/df_ciclo_2022_2025.xlsx
@@ -1,21 +1,173 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/gabrielmachado_prefeitura_sp_gov_br/Documents/Área de Trabalho/IDRGP/IDRGP-2025/R Markdown/resultados/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="6_{F53E8F53-78A1-4DB2-B8EB-2735E931FF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="47">
+  <si>
+    <t>subprefeitura</t>
+  </si>
+  <si>
+    <t>idrgp_alvo</t>
+  </si>
+  <si>
+    <t>valor_2022</t>
+  </si>
+  <si>
+    <t>valor_2023</t>
+  </si>
+  <si>
+    <t>valor_2024</t>
+  </si>
+  <si>
+    <t>valor_2025</t>
+  </si>
+  <si>
+    <t>valor_2022_a_2025</t>
+  </si>
+  <si>
+    <t>idrgp_real_2022_a_2025</t>
+  </si>
+  <si>
+    <t>idrgp_diferenca_ciclo</t>
+  </si>
+  <si>
+    <t>idrgp_var_pct_ciclo</t>
+  </si>
+  <si>
+    <t>status_ciclo</t>
+  </si>
+  <si>
+    <t>status_ciclo_estatistico</t>
+  </si>
+  <si>
+    <t>Aricanduva/Formosa/Carrão</t>
+  </si>
+  <si>
+    <t>Acima do IDRGP Alvo</t>
+  </si>
+  <si>
+    <t>Dentro do IDRGP Alvo</t>
+  </si>
+  <si>
+    <t>Butantã</t>
+  </si>
+  <si>
+    <t>Campo Limpo</t>
+  </si>
+  <si>
+    <t>Abaixo do IDRGP Alvo</t>
+  </si>
+  <si>
+    <t>Capela do Socorro</t>
+  </si>
+  <si>
+    <t>Casa Verde/Cachoeirinha</t>
+  </si>
+  <si>
+    <t>Cidade Ademar</t>
+  </si>
+  <si>
+    <t>Cidade Tiradentes</t>
+  </si>
+  <si>
+    <t>Ermelino Matarazzo</t>
+  </si>
+  <si>
+    <t>Freguesia/Brasilândia</t>
+  </si>
+  <si>
+    <t>Guaianases</t>
+  </si>
+  <si>
+    <t>Ipiranga</t>
+  </si>
+  <si>
+    <t>Itaim Paulista</t>
+  </si>
+  <si>
+    <t>Itaquera</t>
+  </si>
+  <si>
+    <t>Jabaquara</t>
+  </si>
+  <si>
+    <t>Jaçanã/Tremembé</t>
+  </si>
+  <si>
+    <t>Lapa</t>
+  </si>
+  <si>
+    <t>M'Boi Mirim</t>
+  </si>
+  <si>
+    <t>Mooca</t>
+  </si>
+  <si>
+    <t>Parelheiros</t>
+  </si>
+  <si>
+    <t>Penha</t>
+  </si>
+  <si>
+    <t>Perus/Anhanguera</t>
+  </si>
+  <si>
+    <t>Pinheiros</t>
+  </si>
+  <si>
+    <t>Pirituba/Jaraguá</t>
+  </si>
+  <si>
+    <t>Santana/Tucuruvi</t>
+  </si>
+  <si>
+    <t>Santo Amaro</t>
+  </si>
+  <si>
+    <t>Sapopemba</t>
+  </si>
+  <si>
+    <t>São Mateus</t>
+  </si>
+  <si>
+    <t>São Miguel Paulista</t>
+  </si>
+  <si>
+    <t>Sé</t>
+  </si>
+  <si>
+    <t>Vila Maria/Vila Guilherme</t>
+  </si>
+  <si>
+    <t>Vila Mariana</t>
+  </si>
+  <si>
+    <t>Vila Prudente</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +215,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +267,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +301,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +336,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,256 +512,220 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="42.140625" customWidth="1"/>
+    <col min="2" max="2" width="44.7109375" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="34.7109375" customWidth="1"/>
+    <col min="5" max="5" width="30.85546875" customWidth="1"/>
+    <col min="6" max="6" width="42.5703125" customWidth="1"/>
+    <col min="7" max="7" width="42.28515625" customWidth="1"/>
+    <col min="8" max="8" width="26.85546875" customWidth="1"/>
+    <col min="9" max="9" width="36" customWidth="1"/>
+    <col min="10" max="10" width="24.28515625" customWidth="1"/>
+    <col min="11" max="11" width="25.5703125" customWidth="1"/>
+    <col min="12" max="12" width="35.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>subprefeitura</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>idrgp_alvo</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>valor_2022</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>valor_2023</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>valor_2024</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>valor_2025</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>valor_2022_a_2025</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>idrgp_real_2022_a_2025</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>idrgp_diferenca_ciclo</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>idrgp_var_pct_ciclo</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>status_ciclo</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>status_ciclo_estatistico</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Aricanduva/Formosa/Carrão</t>
-        </is>
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
       </c>
       <c r="B2">
-        <v>0.01278087722546964</v>
+        <v>1.2780877225469641E-2</v>
       </c>
       <c r="C2">
-        <v>270800600.28</v>
+        <v>270800600.27999997</v>
       </c>
       <c r="D2">
-        <v>600441154.33</v>
+        <v>600441154.33000004</v>
       </c>
       <c r="E2">
-        <v>737074530.21</v>
+        <v>737074530.21000004</v>
       </c>
       <c r="F2">
-        <v>989484961.0599999</v>
+        <v>989484961.05999994</v>
       </c>
       <c r="G2">
-        <v>2597801245.88</v>
+        <v>2597801245.8800001</v>
       </c>
       <c r="H2">
-        <v>0.01706066772054106</v>
+        <v>1.7060667720541059E-2</v>
       </c>
       <c r="I2">
-        <v>0.004279790495071413</v>
+        <v>4.279790495071413E-3</v>
       </c>
       <c r="J2">
-        <v>0.3348589004941442</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Butantã</t>
-        </is>
+        <v>0.33485890049414418</v>
+      </c>
+      <c r="K2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
       </c>
       <c r="B3">
-        <v>0.03138103348631988</v>
+        <v>3.1381033486319883E-2</v>
       </c>
       <c r="C3">
-        <v>531726447.48</v>
+        <v>531726447.48000002</v>
       </c>
       <c r="D3">
-        <v>1086938304.9</v>
+        <v>1086938304.9000001</v>
       </c>
       <c r="E3">
         <v>1370494139.28</v>
       </c>
       <c r="F3">
-        <v>2120033849.32</v>
+        <v>2120033849.3199999</v>
       </c>
       <c r="G3">
-        <v>5109192740.98</v>
+        <v>5109192740.9799995</v>
       </c>
       <c r="H3">
-        <v>0.03355385244052139</v>
+        <v>3.3553852440521392E-2</v>
       </c>
       <c r="I3">
-        <v>0.002172818954201516</v>
+        <v>2.172818954201516E-3</v>
       </c>
       <c r="J3">
-        <v>0.06923987876781452</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Campo Limpo</t>
-        </is>
+        <v>6.9239878767814525E-2</v>
+      </c>
+      <c r="K3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
       </c>
       <c r="B4">
-        <v>0.07049848664210395</v>
+        <v>7.0498486642103952E-2</v>
       </c>
       <c r="C4">
-        <v>1136043087.37</v>
+        <v>1136043087.3699999</v>
       </c>
       <c r="D4">
-        <v>1893010845.67</v>
+        <v>1893010845.6700001</v>
       </c>
       <c r="E4">
         <v>1802521652.49</v>
       </c>
       <c r="F4">
-        <v>2562583888.81</v>
+        <v>2562583888.8099999</v>
       </c>
       <c r="G4">
-        <v>7394159474.34</v>
+        <v>7394159474.3400002</v>
       </c>
       <c r="H4">
-        <v>0.04856002670122379</v>
+        <v>4.8560026701223787E-2</v>
       </c>
       <c r="I4">
-        <v>-0.02193845994088016</v>
+        <v>-2.1938459940880159E-2</v>
       </c>
       <c r="J4">
-        <v>-0.311190508985732</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Capela do Socorro</t>
-        </is>
+        <v>-0.31119050898573197</v>
+      </c>
+      <c r="K4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>18</v>
       </c>
       <c r="B5">
-        <v>0.08227494643576272</v>
+        <v>8.2274946435762719E-2</v>
       </c>
       <c r="C5">
-        <v>903229166.3</v>
+        <v>903229166.29999995</v>
       </c>
       <c r="D5">
-        <v>1726163460.9</v>
+        <v>1726163460.9000001</v>
       </c>
       <c r="E5">
         <v>2114329482</v>
       </c>
       <c r="F5">
-        <v>3217471932.62</v>
+        <v>3217471932.6199999</v>
       </c>
       <c r="G5">
-        <v>7961194041.82</v>
+        <v>7961194041.8199997</v>
       </c>
       <c r="H5">
-        <v>0.05228394066776743</v>
+        <v>5.2283940667767433E-2</v>
       </c>
       <c r="I5">
-        <v>-0.02999100576799529</v>
+        <v>-2.999100576799529E-2</v>
       </c>
       <c r="J5">
-        <v>-0.3645217294843354</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Casa Verde/Cachoeirinha</t>
-        </is>
+        <v>-0.36452172948433542</v>
+      </c>
+      <c r="K5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
       </c>
       <c r="B6">
-        <v>0.02290605900133662</v>
+        <v>2.2906059001336621E-2</v>
       </c>
       <c r="C6">
         <v>156688314.62</v>
@@ -608,45 +734,39 @@
         <v>842834351.62</v>
       </c>
       <c r="E6">
-        <v>745939592.83</v>
+        <v>745939592.83000004</v>
       </c>
       <c r="F6">
-        <v>990146048.22</v>
+        <v>990146048.22000003</v>
       </c>
       <c r="G6">
         <v>2735608307.29</v>
       </c>
       <c r="H6">
-        <v>0.01796569480372878</v>
+        <v>1.7965694803728779E-2</v>
       </c>
       <c r="I6">
-        <v>-0.004940364197607842</v>
+        <v>-4.9403641976078416E-3</v>
       </c>
       <c r="J6">
-        <v>-0.2156793622735173</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cidade Ademar</t>
-        </is>
+        <v>-0.21567936227351731</v>
+      </c>
+      <c r="K6" t="s">
+        <v>14</v>
+      </c>
+      <c r="L6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>20</v>
       </c>
       <c r="B7">
-        <v>0.05427611013661751</v>
+        <v>5.4276110136617511E-2</v>
       </c>
       <c r="C7">
-        <v>530941174.36</v>
+        <v>530941174.36000001</v>
       </c>
       <c r="D7">
         <v>1031792894.37</v>
@@ -661,39 +781,33 @@
         <v>4265398983.25</v>
       </c>
       <c r="H7">
-        <v>0.02801236425002599</v>
+        <v>2.8012364250025991E-2</v>
       </c>
       <c r="I7">
-        <v>-0.02626374588659152</v>
+        <v>-2.626374588659152E-2</v>
       </c>
       <c r="J7">
-        <v>-0.4838914546470532</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Cidade Tiradentes</t>
-        </is>
+        <v>-0.48389145464705319</v>
+      </c>
+      <c r="K7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>21</v>
       </c>
       <c r="B8">
-        <v>0.02476472440077774</v>
+        <v>2.4764724400777739E-2</v>
       </c>
       <c r="C8">
         <v>323404422.56</v>
       </c>
       <c r="D8">
-        <v>434812479.76</v>
+        <v>434812479.75999999</v>
       </c>
       <c r="E8">
         <v>902673292.38</v>
@@ -702,350 +816,302 @@
         <v>1335237845.73</v>
       </c>
       <c r="G8">
-        <v>2996128040.43</v>
+        <v>2996128040.4299998</v>
       </c>
       <c r="H8">
-        <v>0.01967661884335443</v>
+        <v>1.9676618843354431E-2</v>
       </c>
       <c r="I8">
-        <v>-0.005088105557423311</v>
+        <v>-5.0881055574233114E-3</v>
       </c>
       <c r="J8">
-        <v>-0.2054577904878085</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ermelino Matarazzo</t>
-        </is>
+        <v>-0.20545779048780849</v>
+      </c>
+      <c r="K8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>22</v>
       </c>
       <c r="B9">
-        <v>0.01564514619986043</v>
+        <v>1.5645146199860429E-2</v>
       </c>
       <c r="C9">
-        <v>300184054.28</v>
+        <v>300184054.27999997</v>
       </c>
       <c r="D9">
-        <v>419672736.3</v>
+        <v>419672736.30000001</v>
       </c>
       <c r="E9">
-        <v>500741801.08</v>
+        <v>500741801.07999998</v>
       </c>
       <c r="F9">
-        <v>1144062973.34</v>
+        <v>1144062973.3399999</v>
       </c>
       <c r="G9">
         <v>2364661565</v>
       </c>
       <c r="H9">
-        <v>0.01552955804297244</v>
+        <v>1.552955804297244E-2</v>
       </c>
       <c r="I9">
-        <v>-0.0001155881568879885</v>
+        <v>-1.155881568879885E-4</v>
       </c>
       <c r="J9">
-        <v>-0.007388116123134705</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Freguesia/Brasilândia</t>
-        </is>
+        <v>-7.3881161231347048E-3</v>
+      </c>
+      <c r="K9" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>23</v>
       </c>
       <c r="B10">
-        <v>0.04493881006046815</v>
+        <v>4.4938810060468147E-2</v>
       </c>
       <c r="C10">
-        <v>662096967.22</v>
+        <v>662096967.22000003</v>
       </c>
       <c r="D10">
-        <v>843947046.97</v>
+        <v>843947046.97000003</v>
       </c>
       <c r="E10">
         <v>1100647553.21</v>
       </c>
       <c r="F10">
-        <v>2301085241.03</v>
+        <v>2301085241.0300002</v>
       </c>
       <c r="G10">
-        <v>4907776808.43</v>
+        <v>4907776808.4300003</v>
       </c>
       <c r="H10">
-        <v>0.03223108369356346</v>
+        <v>3.2231083693563457E-2</v>
       </c>
       <c r="I10">
-        <v>-0.01270772636690469</v>
+        <v>-1.270772636690469E-2</v>
       </c>
       <c r="J10">
-        <v>-0.2827784347161307</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Guaianases</t>
-        </is>
+        <v>-0.28277843471613068</v>
+      </c>
+      <c r="K10" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>24</v>
       </c>
       <c r="B11">
-        <v>0.03106350078710079</v>
+        <v>3.1063500787100792E-2</v>
       </c>
       <c r="C11">
-        <v>515288534.05</v>
+        <v>515288534.05000001</v>
       </c>
       <c r="D11">
         <v>686451804.38</v>
       </c>
       <c r="E11">
-        <v>920953728.14</v>
+        <v>920953728.13999999</v>
       </c>
       <c r="F11">
-        <v>1001849833.82</v>
+        <v>1001849833.8200001</v>
       </c>
       <c r="G11">
-        <v>3124543900.39</v>
+        <v>3124543900.3899999</v>
       </c>
       <c r="H11">
-        <v>0.02051997062798372</v>
+        <v>2.0519970627983719E-2</v>
       </c>
       <c r="I11">
-        <v>-0.01054353015911707</v>
+        <v>-1.0543530159117071E-2</v>
       </c>
       <c r="J11">
-        <v>-0.3394186067880443</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Ipiranga</t>
-        </is>
+        <v>-0.33941860678804431</v>
+      </c>
+      <c r="K11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>25</v>
       </c>
       <c r="B12">
-        <v>0.02852737800077722</v>
+        <v>2.8527378000777221E-2</v>
       </c>
       <c r="C12">
-        <v>585362030.52</v>
+        <v>585362030.51999998</v>
       </c>
       <c r="D12">
         <v>1081771738.47</v>
       </c>
       <c r="E12">
-        <v>1187638555.17</v>
+        <v>1187638555.1700001</v>
       </c>
       <c r="F12">
-        <v>1586731737.63</v>
+        <v>1586731737.6300001</v>
       </c>
       <c r="G12">
         <v>4441504061.79</v>
       </c>
       <c r="H12">
-        <v>0.02916890778222873</v>
+        <v>2.9168907782228731E-2</v>
       </c>
       <c r="I12">
-        <v>0.0006415297814515129</v>
+        <v>6.4152978145151293E-4</v>
       </c>
       <c r="J12">
-        <v>0.022488214003896</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Itaim Paulista</t>
-        </is>
+        <v>2.2488214003896001E-2</v>
+      </c>
+      <c r="K12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>26</v>
       </c>
       <c r="B13">
-        <v>0.03440060917127755</v>
+        <v>3.4400609171277553E-2</v>
       </c>
       <c r="C13">
-        <v>677606342.2</v>
+        <v>677606342.20000005</v>
       </c>
       <c r="D13">
-        <v>729781207.34</v>
+        <v>729781207.34000003</v>
       </c>
       <c r="E13">
         <v>809483850.37</v>
       </c>
       <c r="F13">
-        <v>1202924802.61</v>
+        <v>1202924802.6099999</v>
       </c>
       <c r="G13">
         <v>3419796202.52</v>
       </c>
       <c r="H13">
-        <v>0.02245899557392733</v>
+        <v>2.2458995573927332E-2</v>
       </c>
       <c r="I13">
-        <v>-0.01194161359735021</v>
+        <v>-1.1941613597350209E-2</v>
       </c>
       <c r="J13">
-        <v>-0.347133782948261</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Itaquera</t>
-        </is>
+        <v>-0.34713378294826103</v>
+      </c>
+      <c r="K13" t="s">
+        <v>17</v>
+      </c>
+      <c r="L13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>27</v>
       </c>
       <c r="B14">
-        <v>0.04982071041328871</v>
+        <v>4.9820710413288713E-2</v>
       </c>
       <c r="C14">
-        <v>892661593.1899999</v>
+        <v>892661593.18999994</v>
       </c>
       <c r="D14">
-        <v>1104357795.92</v>
+        <v>1104357795.9200001</v>
       </c>
       <c r="E14">
-        <v>1381059096.62</v>
+        <v>1381059096.6199999</v>
       </c>
       <c r="F14">
-        <v>2039768606.41</v>
+        <v>2039768606.4100001</v>
       </c>
       <c r="G14">
-        <v>5417847092.14</v>
+        <v>5417847092.1400003</v>
       </c>
       <c r="H14">
-        <v>0.03558089332133988</v>
+        <v>3.5580893321339881E-2</v>
       </c>
       <c r="I14">
-        <v>-0.01423981709194883</v>
+        <v>-1.4239817091948831E-2</v>
       </c>
       <c r="J14">
-        <v>-0.2858212372690421</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Jabaquara</t>
-        </is>
+        <v>-0.28582123726904213</v>
+      </c>
+      <c r="K14" t="s">
+        <v>14</v>
+      </c>
+      <c r="L14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>28</v>
       </c>
       <c r="B15">
-        <v>0.0146420577822676</v>
+        <v>1.46420577822676E-2</v>
       </c>
       <c r="C15">
-        <v>289068585.26</v>
+        <v>289068585.25999999</v>
       </c>
       <c r="D15">
-        <v>1149596326.06</v>
+        <v>1149596326.0599999</v>
       </c>
       <c r="E15">
-        <v>1278748563.6</v>
+        <v>1278748563.5999999</v>
       </c>
       <c r="F15">
-        <v>1532982112.9</v>
+        <v>1532982112.9000001</v>
       </c>
       <c r="G15">
-        <v>4250395587.82</v>
+        <v>4250395587.8200002</v>
       </c>
       <c r="H15">
-        <v>0.02791383171428368</v>
+        <v>2.7913831714283681E-2</v>
       </c>
       <c r="I15">
-        <v>0.01327177393201608</v>
+        <v>1.3271773932016079E-2</v>
       </c>
       <c r="J15">
-        <v>0.9064145306193908</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Jaçanã/Tremembé</t>
-        </is>
+        <v>0.90641453061939081</v>
+      </c>
+      <c r="K15" t="s">
+        <v>13</v>
+      </c>
+      <c r="L15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>29</v>
       </c>
       <c r="B16">
-        <v>0.03619588619759224</v>
+        <v>3.6195886197592238E-2</v>
       </c>
       <c r="C16">
-        <v>418653600.77</v>
+        <v>418653600.76999998</v>
       </c>
       <c r="D16">
-        <v>716643418.8</v>
+        <v>716643418.79999995</v>
       </c>
       <c r="E16">
         <v>1018298108.3</v>
@@ -1054,438 +1120,378 @@
         <v>1078973096.78</v>
       </c>
       <c r="G16">
-        <v>3232568224.65</v>
+        <v>3232568224.6500001</v>
       </c>
       <c r="H16">
-        <v>0.02122940407862152</v>
+        <v>2.1229404078621519E-2</v>
       </c>
       <c r="I16">
-        <v>-0.01496648211897071</v>
+        <v>-1.496648211897071E-2</v>
       </c>
       <c r="J16">
-        <v>-0.4134857214786549</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Lapa</t>
-        </is>
+        <v>-0.41348572147865492</v>
+      </c>
+      <c r="K16" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>30</v>
       </c>
       <c r="B17">
-        <v>0.01196759457375883</v>
+        <v>1.196759457375883E-2</v>
       </c>
       <c r="C17">
         <v>439828459.44</v>
       </c>
       <c r="D17">
-        <v>1105161010.6</v>
+        <v>1105161010.5999999</v>
       </c>
       <c r="E17">
         <v>1270053924.95</v>
       </c>
       <c r="F17">
-        <v>1635541987.13</v>
+        <v>1635541987.1300001</v>
       </c>
       <c r="G17">
-        <v>4450585382.12</v>
+        <v>4450585382.1199999</v>
       </c>
       <c r="H17">
-        <v>0.02922854798328708</v>
+        <v>2.9228547983287081E-2</v>
       </c>
       <c r="I17">
-        <v>0.01726095340952825</v>
+        <v>1.7260953409528251E-2</v>
       </c>
       <c r="J17">
-        <v>1.442307667020747</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>M'Boi Mirim</t>
-        </is>
+        <v>1.4423076670207471</v>
+      </c>
+      <c r="K17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>31</v>
       </c>
       <c r="B18">
-        <v>0.0768001000600067</v>
+        <v>7.6800100060006704E-2</v>
       </c>
       <c r="C18">
-        <v>407603040.74</v>
+        <v>407603040.74000001</v>
       </c>
       <c r="D18">
-        <v>1414739277.9</v>
+        <v>1414739277.9000001</v>
       </c>
       <c r="E18">
         <v>1550313121.75</v>
       </c>
       <c r="F18">
-        <v>3036975936.59</v>
+        <v>3036975936.5900002</v>
       </c>
       <c r="G18">
-        <v>6409631376.98</v>
+        <v>6409631376.9799995</v>
       </c>
       <c r="H18">
-        <v>0.04209428696950479</v>
+        <v>4.2094286969504791E-2</v>
       </c>
       <c r="I18">
-        <v>-0.03470581309050191</v>
+        <v>-3.4705813090501907E-2</v>
       </c>
       <c r="J18">
-        <v>-0.4518980191872797</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Mooca</t>
-        </is>
+        <v>-0.45189801918727968</v>
+      </c>
+      <c r="K18" t="s">
+        <v>17</v>
+      </c>
+      <c r="L18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>32</v>
       </c>
       <c r="B19">
-        <v>0.01518693116727706</v>
+        <v>1.5186931167277059E-2</v>
       </c>
       <c r="C19">
-        <v>444011947.82</v>
+        <v>444011947.81999999</v>
       </c>
       <c r="D19">
-        <v>1177863319.16</v>
+        <v>1177863319.1600001</v>
       </c>
       <c r="E19">
-        <v>1879548379.37</v>
+        <v>1879548379.3699999</v>
       </c>
       <c r="F19">
-        <v>2415839399.78</v>
+        <v>2415839399.7800002</v>
       </c>
       <c r="G19">
-        <v>5917263046.13</v>
+        <v>5917263046.1300001</v>
       </c>
       <c r="H19">
-        <v>0.03886073224622813</v>
+        <v>3.886073224622813E-2</v>
       </c>
       <c r="I19">
-        <v>0.02367380107895107</v>
+        <v>2.3673801078951069E-2</v>
       </c>
       <c r="J19">
-        <v>1.55882717964512</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Parelheiros</t>
-        </is>
+        <v>1.5588271796451201</v>
+      </c>
+      <c r="K19" t="s">
+        <v>13</v>
+      </c>
+      <c r="L19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>33</v>
       </c>
       <c r="B20">
-        <v>0.04188065349285796</v>
+        <v>4.188065349285796E-2</v>
       </c>
       <c r="C20">
-        <v>254092379.92</v>
+        <v>254092379.91999999</v>
       </c>
       <c r="D20">
         <v>599141447.25</v>
       </c>
       <c r="E20">
-        <v>891442908.4</v>
+        <v>891442908.39999998</v>
       </c>
       <c r="F20">
-        <v>1294481417.88</v>
+        <v>1294481417.8800001</v>
       </c>
       <c r="G20">
-        <v>3039158153.45</v>
+        <v>3039158153.4499998</v>
       </c>
       <c r="H20">
-        <v>0.01995921261813833</v>
+        <v>1.9959212618138329E-2</v>
       </c>
       <c r="I20">
-        <v>-0.02192144087471963</v>
+        <v>-2.192144087471963E-2</v>
       </c>
       <c r="J20">
-        <v>-0.5234264283497382</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Penha</t>
-        </is>
+        <v>-0.52342642834973818</v>
+      </c>
+      <c r="K20" t="s">
+        <v>17</v>
+      </c>
+      <c r="L20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>34</v>
       </c>
       <c r="B21">
-        <v>0.03328667005479251</v>
+        <v>3.3286670054792508E-2</v>
       </c>
       <c r="C21">
-        <v>413735667.28</v>
+        <v>413735667.27999997</v>
       </c>
       <c r="D21">
         <v>1002662305.98</v>
       </c>
       <c r="E21">
-        <v>1355941790.68</v>
+        <v>1355941790.6800001</v>
       </c>
       <c r="F21">
         <v>1705356170.99</v>
       </c>
       <c r="G21">
-        <v>4477695934.93</v>
+        <v>4477695934.9300003</v>
       </c>
       <c r="H21">
-        <v>0.02940659244836891</v>
+        <v>2.940659244836891E-2</v>
       </c>
       <c r="I21">
-        <v>-0.003880077606423601</v>
+        <v>-3.880077606423601E-3</v>
       </c>
       <c r="J21">
         <v>-0.1165655080558279</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Perus/Anhanguera</t>
-        </is>
+      <c r="K21" t="s">
+        <v>14</v>
+      </c>
+      <c r="L21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>35</v>
       </c>
       <c r="B22">
-        <v>0.021319194803451</v>
+        <v>2.1319194803451E-2</v>
       </c>
       <c r="C22">
         <v>318856012.44</v>
       </c>
       <c r="D22">
-        <v>378277168.48</v>
+        <v>378277168.48000002</v>
       </c>
       <c r="E22">
         <v>643891246.63</v>
       </c>
       <c r="F22">
-        <v>918890507.58</v>
+        <v>918890507.58000004</v>
       </c>
       <c r="G22">
-        <v>2259914935.13</v>
+        <v>2259914935.1300001</v>
       </c>
       <c r="H22">
-        <v>0.01484165035569546</v>
+        <v>1.4841650355695461E-2</v>
       </c>
       <c r="I22">
-        <v>-0.006477544447755532</v>
+        <v>-6.4775444477555323E-3</v>
       </c>
       <c r="J22">
         <v>-0.3038362615227379</v>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Pinheiros</t>
-        </is>
+      <c r="K22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>36</v>
       </c>
       <c r="B23">
-        <v>0.006306371387863901</v>
+        <v>6.3063713878639006E-3</v>
       </c>
       <c r="C23">
-        <v>179126600.35</v>
+        <v>179126600.34999999</v>
       </c>
       <c r="D23">
-        <v>681661685.0599999</v>
+        <v>681661685.05999994</v>
       </c>
       <c r="E23">
-        <v>623666594.01</v>
+        <v>623666594.00999999</v>
       </c>
       <c r="F23">
-        <v>997429393.05</v>
+        <v>997429393.04999995</v>
       </c>
       <c r="G23">
-        <v>2481884272.47</v>
+        <v>2481884272.4699998</v>
       </c>
       <c r="H23">
-        <v>0.01629940048747031</v>
+        <v>1.6299400487470309E-2</v>
       </c>
       <c r="I23">
-        <v>0.009993029099606409</v>
+        <v>9.9930290996064087E-3</v>
       </c>
       <c r="J23">
-        <v>1.584592546965626</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Pirituba/Jaraguá</t>
-        </is>
+        <v>1.5845925469656259</v>
+      </c>
+      <c r="K23" t="s">
+        <v>13</v>
+      </c>
+      <c r="L23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>37</v>
       </c>
       <c r="B24">
-        <v>0.03550998362496413</v>
+        <v>3.5509983624964131E-2</v>
       </c>
       <c r="C24">
-        <v>373444861.42</v>
+        <v>373444861.42000002</v>
       </c>
       <c r="D24">
-        <v>624679391.73</v>
+        <v>624679391.73000002</v>
       </c>
       <c r="E24">
-        <v>856333446.46</v>
+        <v>856333446.46000004</v>
       </c>
       <c r="F24">
-        <v>1785675753.86</v>
+        <v>1785675753.8599999</v>
       </c>
       <c r="G24">
-        <v>3640133453.47</v>
+        <v>3640133453.4699998</v>
       </c>
       <c r="H24">
-        <v>0.02390602722458852</v>
+        <v>2.3906027224588521E-2</v>
       </c>
       <c r="I24">
-        <v>-0.01160395640037561</v>
+        <v>-1.160395640037561E-2</v>
       </c>
       <c r="J24">
-        <v>-0.3267801112760251</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Santana/Tucuruvi</t>
-        </is>
+        <v>-0.32678011127602508</v>
+      </c>
+      <c r="K24" t="s">
+        <v>17</v>
+      </c>
+      <c r="L24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>38</v>
       </c>
       <c r="B25">
-        <v>0.01442360309469943</v>
+        <v>1.4423603094699431E-2</v>
       </c>
       <c r="C25">
-        <v>166699640.05</v>
+        <v>166699640.05000001</v>
       </c>
       <c r="D25">
-        <v>1743044894.91</v>
+        <v>1743044894.9100001</v>
       </c>
       <c r="E25">
-        <v>1554935421.67</v>
+        <v>1554935421.6700001</v>
       </c>
       <c r="F25">
-        <v>1376552981.17</v>
+        <v>1376552981.1700001</v>
       </c>
       <c r="G25">
-        <v>4841232937.8</v>
+        <v>4841232937.8000002</v>
       </c>
       <c r="H25">
-        <v>0.03179406686348163</v>
+        <v>3.1794066863481629E-2</v>
       </c>
       <c r="I25">
-        <v>0.0173704637687822</v>
+        <v>1.73704637687822E-2</v>
       </c>
       <c r="J25">
         <v>1.204308219987398</v>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Santo Amaro</t>
-        </is>
+      <c r="K25" t="s">
+        <v>13</v>
+      </c>
+      <c r="L25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>39</v>
       </c>
       <c r="B26">
-        <v>0.00780842708567104</v>
+        <v>7.8084270856710403E-3</v>
       </c>
       <c r="C26">
-        <v>214276208.71</v>
+        <v>214276208.71000001</v>
       </c>
       <c r="D26">
-        <v>790575300.34</v>
+        <v>790575300.34000003</v>
       </c>
       <c r="E26">
         <v>849590055.38</v>
@@ -1494,42 +1500,36 @@
         <v>1665436605.22</v>
       </c>
       <c r="G26">
-        <v>3519878169.65</v>
+        <v>3519878169.6500001</v>
       </c>
       <c r="H26">
-        <v>0.0231162687924736</v>
+        <v>2.3116268792473599E-2</v>
       </c>
       <c r="I26">
-        <v>0.01530784170680256</v>
+        <v>1.530784170680256E-2</v>
       </c>
       <c r="J26">
         <v>1.960425773187205</v>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Sapopemba</t>
-        </is>
+      <c r="K26" t="s">
+        <v>13</v>
+      </c>
+      <c r="L26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>40</v>
       </c>
       <c r="B27">
-        <v>0.02854078087441063</v>
+        <v>2.8540780874410629E-2</v>
       </c>
       <c r="C27">
-        <v>297798794.47</v>
+        <v>297798794.47000003</v>
       </c>
       <c r="D27">
-        <v>746739859.46</v>
+        <v>746739859.46000004</v>
       </c>
       <c r="E27">
         <v>730973098.37</v>
@@ -1541,171 +1541,147 @@
         <v>2854148107.75</v>
       </c>
       <c r="H27">
-        <v>0.01874418705771267</v>
+        <v>1.874418705771267E-2</v>
       </c>
       <c r="I27">
-        <v>-0.009796593816697955</v>
+        <v>-9.7965938166979551E-3</v>
       </c>
       <c r="J27">
-        <v>-0.3432489762563393</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>São Mateus</t>
-        </is>
+        <v>-0.34324897625633932</v>
+      </c>
+      <c r="K27" t="s">
+        <v>17</v>
+      </c>
+      <c r="L27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>41</v>
       </c>
       <c r="B28">
-        <v>0.05776210461891745</v>
+        <v>5.7762104618917447E-2</v>
       </c>
       <c r="C28">
-        <v>609449214.6</v>
+        <v>609449214.60000002</v>
       </c>
       <c r="D28">
         <v>1096779160.03</v>
       </c>
       <c r="E28">
-        <v>1424727936.6</v>
+        <v>1424727936.5999999</v>
       </c>
       <c r="F28">
-        <v>1956937590.38</v>
+        <v>1956937590.3800001</v>
       </c>
       <c r="G28">
-        <v>5087893901.610001</v>
+        <v>5087893901.6100006</v>
       </c>
       <c r="H28">
-        <v>0.0334139755265731</v>
+        <v>3.3413975526573103E-2</v>
       </c>
       <c r="I28">
-        <v>-0.02434812909234436</v>
+        <v>-2.4348129092344361E-2</v>
       </c>
       <c r="J28">
-        <v>-0.4215242718903665</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>São Miguel Paulista</t>
-        </is>
+        <v>-0.42152427189036651</v>
+      </c>
+      <c r="K28" t="s">
+        <v>17</v>
+      </c>
+      <c r="L28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>42</v>
       </c>
       <c r="B29">
-        <v>0.03997675152969091</v>
+        <v>3.9976751529690907E-2</v>
       </c>
       <c r="C29">
-        <v>451987454.6</v>
+        <v>451987454.60000002</v>
       </c>
       <c r="D29">
-        <v>646056157.14</v>
+        <v>646056157.13999999</v>
       </c>
       <c r="E29">
-        <v>757654983.4</v>
+        <v>757654983.39999998</v>
       </c>
       <c r="F29">
         <v>1362970185.21</v>
       </c>
       <c r="G29">
-        <v>3218668780.35</v>
+        <v>3218668780.3499999</v>
       </c>
       <c r="H29">
-        <v>0.02113812157535899</v>
+        <v>2.1138121575358989E-2</v>
       </c>
       <c r="I29">
-        <v>-0.01883862995433193</v>
+        <v>-1.8838629954331929E-2</v>
       </c>
       <c r="J29">
-        <v>-0.4712396388771206</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Abaixo do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Sé</t>
-        </is>
+        <v>-0.47123963887712061</v>
+      </c>
+      <c r="K29" t="s">
+        <v>17</v>
+      </c>
+      <c r="L29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>43</v>
       </c>
       <c r="B30">
-        <v>0.01774539803593836</v>
+        <v>1.7745398035938359E-2</v>
       </c>
       <c r="C30">
         <v>2593261890.04</v>
       </c>
       <c r="D30">
-        <v>4671432106.8</v>
+        <v>4671432106.8000002</v>
       </c>
       <c r="E30">
         <v>11259293445.76</v>
       </c>
       <c r="F30">
-        <v>6837566518.55</v>
+        <v>6837566518.5500002</v>
       </c>
       <c r="G30">
-        <v>25361553961.15</v>
+        <v>25361553961.150002</v>
       </c>
       <c r="H30">
-        <v>0.1665581790346631</v>
+        <v>0.16655817903466311</v>
       </c>
       <c r="I30">
-        <v>0.1488127809987247</v>
+        <v>0.14881278099872469</v>
       </c>
       <c r="J30">
-        <v>8.385992847122722</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Vila Maria/Vila Guilherme</t>
-        </is>
+        <v>8.3859928471227221</v>
+      </c>
+      <c r="K30" t="s">
+        <v>13</v>
+      </c>
+      <c r="L30" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>44</v>
       </c>
       <c r="B31">
-        <v>0.01471389456597418</v>
+        <v>1.4713894565974181E-2</v>
       </c>
       <c r="C31">
-        <v>310244568.84</v>
+        <v>310244568.83999997</v>
       </c>
       <c r="D31">
-        <v>885501416.5700001</v>
+        <v>885501416.57000005</v>
       </c>
       <c r="E31">
         <v>1250274401.01</v>
@@ -1714,114 +1690,98 @@
         <v>1594437761.49</v>
       </c>
       <c r="G31">
-        <v>4040458147.91</v>
+        <v>4040458147.9099998</v>
       </c>
       <c r="H31">
-        <v>0.02653509925348209</v>
+        <v>2.6535099253482089E-2</v>
       </c>
       <c r="I31">
-        <v>0.0118212046875079</v>
+        <v>1.18212046875079E-2</v>
       </c>
       <c r="J31">
-        <v>0.8034041996497913</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Vila Mariana</t>
-        </is>
+        <v>0.80340419964979126</v>
+      </c>
+      <c r="K31" t="s">
+        <v>13</v>
+      </c>
+      <c r="L31" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>45</v>
       </c>
       <c r="B32">
-        <v>0.007949529934269608</v>
+        <v>7.9495299342696082E-3</v>
       </c>
       <c r="C32">
         <v>270403481.87</v>
       </c>
       <c r="D32">
-        <v>918101079.46</v>
+        <v>918101079.46000004</v>
       </c>
       <c r="E32">
-        <v>1373080195.35</v>
+        <v>1373080195.3499999</v>
       </c>
       <c r="F32">
-        <v>1939351672.66</v>
+        <v>1939351672.6600001</v>
       </c>
       <c r="G32">
-        <v>4500936429.34</v>
+        <v>4500936429.3400002</v>
       </c>
       <c r="H32">
-        <v>0.02955922088883137</v>
+        <v>2.955922088883137E-2</v>
       </c>
       <c r="I32">
-        <v>0.02160969095456176</v>
+        <v>2.160969095456176E-2</v>
       </c>
       <c r="J32">
-        <v>2.718360850671761</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Acima do IDRGP Alvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Vila Prudente</t>
-        </is>
+        <v>2.7183608506717611</v>
+      </c>
+      <c r="K32" t="s">
+        <v>13</v>
+      </c>
+      <c r="L32" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>46</v>
       </c>
       <c r="B33">
-        <v>0.01470567515443555</v>
+        <v>1.4705675154435551E-2</v>
       </c>
       <c r="C33">
         <v>190978482.88</v>
       </c>
       <c r="D33">
-        <v>490592596.61</v>
+        <v>490592596.61000001</v>
       </c>
       <c r="E33">
-        <v>490806393.49</v>
+        <v>490806393.49000001</v>
       </c>
       <c r="F33">
-        <v>776448481.35</v>
+        <v>776448481.35000002</v>
       </c>
       <c r="G33">
-        <v>1948825954.33</v>
+        <v>1948825954.3299999</v>
       </c>
       <c r="H33">
-        <v>0.01279862041205837</v>
+        <v>1.279862041205837E-2</v>
       </c>
       <c r="I33">
-        <v>-0.001907054742377181</v>
+        <v>-1.907054742377181E-3</v>
       </c>
       <c r="J33">
-        <v>-0.129681549629632</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Dentro do IDRGP Alvo</t>
-        </is>
+        <v>-0.12968154962963199</v>
+      </c>
+      <c r="K33" t="s">
+        <v>14</v>
+      </c>
+      <c r="L33" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/R Markdown/resultados/df_ciclo_2022_2025.xlsx
+++ b/R Markdown/resultados/df_ciclo_2022_2025.xlsx
@@ -1,173 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/gabrielmachado_prefeitura_sp_gov_br/Documents/Área de Trabalho/IDRGP/IDRGP-2025/R Markdown/resultados/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="6_{F53E8F53-78A1-4DB2-B8EB-2735E931FF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="47">
-  <si>
-    <t>subprefeitura</t>
-  </si>
-  <si>
-    <t>idrgp_alvo</t>
-  </si>
-  <si>
-    <t>valor_2022</t>
-  </si>
-  <si>
-    <t>valor_2023</t>
-  </si>
-  <si>
-    <t>valor_2024</t>
-  </si>
-  <si>
-    <t>valor_2025</t>
-  </si>
-  <si>
-    <t>valor_2022_a_2025</t>
-  </si>
-  <si>
-    <t>idrgp_real_2022_a_2025</t>
-  </si>
-  <si>
-    <t>idrgp_diferenca_ciclo</t>
-  </si>
-  <si>
-    <t>idrgp_var_pct_ciclo</t>
-  </si>
-  <si>
-    <t>status_ciclo</t>
-  </si>
-  <si>
-    <t>status_ciclo_estatistico</t>
-  </si>
-  <si>
-    <t>Aricanduva/Formosa/Carrão</t>
-  </si>
-  <si>
-    <t>Acima do IDRGP Alvo</t>
-  </si>
-  <si>
-    <t>Dentro do IDRGP Alvo</t>
-  </si>
-  <si>
-    <t>Butantã</t>
-  </si>
-  <si>
-    <t>Campo Limpo</t>
-  </si>
-  <si>
-    <t>Abaixo do IDRGP Alvo</t>
-  </si>
-  <si>
-    <t>Capela do Socorro</t>
-  </si>
-  <si>
-    <t>Casa Verde/Cachoeirinha</t>
-  </si>
-  <si>
-    <t>Cidade Ademar</t>
-  </si>
-  <si>
-    <t>Cidade Tiradentes</t>
-  </si>
-  <si>
-    <t>Ermelino Matarazzo</t>
-  </si>
-  <si>
-    <t>Freguesia/Brasilândia</t>
-  </si>
-  <si>
-    <t>Guaianases</t>
-  </si>
-  <si>
-    <t>Ipiranga</t>
-  </si>
-  <si>
-    <t>Itaim Paulista</t>
-  </si>
-  <si>
-    <t>Itaquera</t>
-  </si>
-  <si>
-    <t>Jabaquara</t>
-  </si>
-  <si>
-    <t>Jaçanã/Tremembé</t>
-  </si>
-  <si>
-    <t>Lapa</t>
-  </si>
-  <si>
-    <t>M'Boi Mirim</t>
-  </si>
-  <si>
-    <t>Mooca</t>
-  </si>
-  <si>
-    <t>Parelheiros</t>
-  </si>
-  <si>
-    <t>Penha</t>
-  </si>
-  <si>
-    <t>Perus/Anhanguera</t>
-  </si>
-  <si>
-    <t>Pinheiros</t>
-  </si>
-  <si>
-    <t>Pirituba/Jaraguá</t>
-  </si>
-  <si>
-    <t>Santana/Tucuruvi</t>
-  </si>
-  <si>
-    <t>Santo Amaro</t>
-  </si>
-  <si>
-    <t>Sapopemba</t>
-  </si>
-  <si>
-    <t>São Mateus</t>
-  </si>
-  <si>
-    <t>São Miguel Paulista</t>
-  </si>
-  <si>
-    <t>Sé</t>
-  </si>
-  <si>
-    <t>Vila Maria/Vila Guilherme</t>
-  </si>
-  <si>
-    <t>Vila Mariana</t>
-  </si>
-  <si>
-    <t>Vila Prudente</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -215,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -267,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -301,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -336,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -512,220 +350,256 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="42.140625" customWidth="1"/>
-    <col min="2" max="2" width="44.7109375" customWidth="1"/>
-    <col min="3" max="3" width="38" customWidth="1"/>
-    <col min="4" max="4" width="34.7109375" customWidth="1"/>
-    <col min="5" max="5" width="30.85546875" customWidth="1"/>
-    <col min="6" max="6" width="42.5703125" customWidth="1"/>
-    <col min="7" max="7" width="42.28515625" customWidth="1"/>
-    <col min="8" max="8" width="26.85546875" customWidth="1"/>
-    <col min="9" max="9" width="36" customWidth="1"/>
-    <col min="10" max="10" width="24.28515625" customWidth="1"/>
-    <col min="11" max="11" width="25.5703125" customWidth="1"/>
-    <col min="12" max="12" width="35.85546875" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>subprefeitura</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>idrgp_alvo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>valor_2022</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>valor_2023</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>valor_2024</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>valor_2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>valor_2022_a_2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>idrgp_real_2022_a_2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>idrgp_diferenca_ciclo</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>idrgp_var_pct_ciclo</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>status_ciclo</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>status_ciclo_estatistico</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Aricanduva/Formosa/Carrão</t>
+        </is>
       </c>
       <c r="B2">
-        <v>1.2780877225469641E-2</v>
+        <v>0.01278087722546964</v>
       </c>
       <c r="C2">
-        <v>270800600.27999997</v>
+        <v>270800600.28</v>
       </c>
       <c r="D2">
-        <v>600441154.33000004</v>
+        <v>600441154.33</v>
       </c>
       <c r="E2">
-        <v>737074530.21000004</v>
+        <v>737074530.21</v>
       </c>
       <c r="F2">
-        <v>989484961.05999994</v>
+        <v>989484961.0599999</v>
       </c>
       <c r="G2">
-        <v>2597801245.8800001</v>
+        <v>2597801245.88</v>
       </c>
       <c r="H2">
-        <v>1.7060667720541059E-2</v>
+        <v>0.01706066772054106</v>
       </c>
       <c r="I2">
-        <v>4.279790495071413E-3</v>
+        <v>0.004279790495071413</v>
       </c>
       <c r="J2">
-        <v>0.33485890049414418</v>
-      </c>
-      <c r="K2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>15</v>
+        <v>0.3348589004941442</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Butantã</t>
+        </is>
       </c>
       <c r="B3">
-        <v>3.1381033486319883E-2</v>
+        <v>0.03138103348631988</v>
       </c>
       <c r="C3">
-        <v>531726447.48000002</v>
+        <v>531726447.48</v>
       </c>
       <c r="D3">
-        <v>1086938304.9000001</v>
+        <v>1086938304.9</v>
       </c>
       <c r="E3">
         <v>1370494139.28</v>
       </c>
       <c r="F3">
-        <v>2120033849.3199999</v>
+        <v>2120033849.32</v>
       </c>
       <c r="G3">
-        <v>5109192740.9799995</v>
+        <v>5109192740.98</v>
       </c>
       <c r="H3">
-        <v>3.3553852440521392E-2</v>
+        <v>0.03355385244052139</v>
       </c>
       <c r="I3">
-        <v>2.172818954201516E-3</v>
+        <v>0.002172818954201516</v>
       </c>
       <c r="J3">
-        <v>6.9239878767814525E-2</v>
-      </c>
-      <c r="K3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>16</v>
+        <v>0.06923987876781452</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Campo Limpo</t>
+        </is>
       </c>
       <c r="B4">
-        <v>7.0498486642103952E-2</v>
+        <v>0.07049848664210395</v>
       </c>
       <c r="C4">
-        <v>1136043087.3699999</v>
+        <v>1136043087.37</v>
       </c>
       <c r="D4">
-        <v>1893010845.6700001</v>
+        <v>1893010845.67</v>
       </c>
       <c r="E4">
         <v>1802521652.49</v>
       </c>
       <c r="F4">
-        <v>2562583888.8099999</v>
+        <v>2562583888.81</v>
       </c>
       <c r="G4">
-        <v>7394159474.3400002</v>
+        <v>7394159474.34</v>
       </c>
       <c r="H4">
-        <v>4.8560026701223787E-2</v>
+        <v>0.04856002670122379</v>
       </c>
       <c r="I4">
-        <v>-2.1938459940880159E-2</v>
+        <v>-0.02193845994088016</v>
       </c>
       <c r="J4">
-        <v>-0.31119050898573197</v>
-      </c>
-      <c r="K4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>18</v>
+        <v>-0.311190508985732</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Capela do Socorro</t>
+        </is>
       </c>
       <c r="B5">
-        <v>8.2274946435762719E-2</v>
+        <v>0.08227494643576272</v>
       </c>
       <c r="C5">
-        <v>903229166.29999995</v>
+        <v>903229166.3</v>
       </c>
       <c r="D5">
-        <v>1726163460.9000001</v>
+        <v>1726163460.9</v>
       </c>
       <c r="E5">
         <v>2114329482</v>
       </c>
       <c r="F5">
-        <v>3217471932.6199999</v>
+        <v>3217471932.62</v>
       </c>
       <c r="G5">
-        <v>7961194041.8199997</v>
+        <v>7961194041.82</v>
       </c>
       <c r="H5">
-        <v>5.2283940667767433E-2</v>
+        <v>0.05228394066776743</v>
       </c>
       <c r="I5">
-        <v>-2.999100576799529E-2</v>
+        <v>-0.02999100576799529</v>
       </c>
       <c r="J5">
-        <v>-0.36452172948433542</v>
-      </c>
-      <c r="K5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>19</v>
+        <v>-0.3645217294843354</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Casa Verde/Cachoeirinha</t>
+        </is>
       </c>
       <c r="B6">
-        <v>2.2906059001336621E-2</v>
+        <v>0.02290605900133662</v>
       </c>
       <c r="C6">
         <v>156688314.62</v>
@@ -734,39 +608,45 @@
         <v>842834351.62</v>
       </c>
       <c r="E6">
-        <v>745939592.83000004</v>
+        <v>745939592.83</v>
       </c>
       <c r="F6">
-        <v>990146048.22000003</v>
+        <v>990146048.22</v>
       </c>
       <c r="G6">
         <v>2735608307.29</v>
       </c>
       <c r="H6">
-        <v>1.7965694803728779E-2</v>
+        <v>0.01796569480372878</v>
       </c>
       <c r="I6">
-        <v>-4.9403641976078416E-3</v>
+        <v>-0.004940364197607842</v>
       </c>
       <c r="J6">
-        <v>-0.21567936227351731</v>
-      </c>
-      <c r="K6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>20</v>
+        <v>-0.2156793622735173</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cidade Ademar</t>
+        </is>
       </c>
       <c r="B7">
-        <v>5.4276110136617511E-2</v>
+        <v>0.05427611013661751</v>
       </c>
       <c r="C7">
-        <v>530941174.36000001</v>
+        <v>530941174.36</v>
       </c>
       <c r="D7">
         <v>1031792894.37</v>
@@ -781,33 +661,39 @@
         <v>4265398983.25</v>
       </c>
       <c r="H7">
-        <v>2.8012364250025991E-2</v>
+        <v>0.02801236425002599</v>
       </c>
       <c r="I7">
-        <v>-2.626374588659152E-2</v>
+        <v>-0.02626374588659152</v>
       </c>
       <c r="J7">
-        <v>-0.48389145464705319</v>
-      </c>
-      <c r="K7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>21</v>
+        <v>-0.4838914546470532</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cidade Tiradentes</t>
+        </is>
       </c>
       <c r="B8">
-        <v>2.4764724400777739E-2</v>
+        <v>0.02476472440077774</v>
       </c>
       <c r="C8">
         <v>323404422.56</v>
       </c>
       <c r="D8">
-        <v>434812479.75999999</v>
+        <v>434812479.76</v>
       </c>
       <c r="E8">
         <v>902673292.38</v>
@@ -816,302 +702,350 @@
         <v>1335237845.73</v>
       </c>
       <c r="G8">
-        <v>2996128040.4299998</v>
+        <v>2996128040.43</v>
       </c>
       <c r="H8">
-        <v>1.9676618843354431E-2</v>
+        <v>0.01967661884335443</v>
       </c>
       <c r="I8">
-        <v>-5.0881055574233114E-3</v>
+        <v>-0.005088105557423311</v>
       </c>
       <c r="J8">
-        <v>-0.20545779048780849</v>
-      </c>
-      <c r="K8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>22</v>
+        <v>-0.2054577904878085</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ermelino Matarazzo</t>
+        </is>
       </c>
       <c r="B9">
-        <v>1.5645146199860429E-2</v>
+        <v>0.01564514619986043</v>
       </c>
       <c r="C9">
-        <v>300184054.27999997</v>
+        <v>300184054.28</v>
       </c>
       <c r="D9">
-        <v>419672736.30000001</v>
+        <v>419672736.3</v>
       </c>
       <c r="E9">
-        <v>500741801.07999998</v>
+        <v>500741801.08</v>
       </c>
       <c r="F9">
-        <v>1144062973.3399999</v>
+        <v>1144062973.34</v>
       </c>
       <c r="G9">
         <v>2364661565</v>
       </c>
       <c r="H9">
-        <v>1.552955804297244E-2</v>
+        <v>0.01552955804297244</v>
       </c>
       <c r="I9">
-        <v>-1.155881568879885E-4</v>
+        <v>-0.0001155881568879885</v>
       </c>
       <c r="J9">
-        <v>-7.3881161231347048E-3</v>
-      </c>
-      <c r="K9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>23</v>
+        <v>-0.007388116123134705</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Freguesia/Brasilândia</t>
+        </is>
       </c>
       <c r="B10">
-        <v>4.4938810060468147E-2</v>
+        <v>0.04493881006046815</v>
       </c>
       <c r="C10">
-        <v>662096967.22000003</v>
+        <v>662096967.22</v>
       </c>
       <c r="D10">
-        <v>843947046.97000003</v>
+        <v>843947046.97</v>
       </c>
       <c r="E10">
         <v>1100647553.21</v>
       </c>
       <c r="F10">
-        <v>2301085241.0300002</v>
+        <v>2301085241.03</v>
       </c>
       <c r="G10">
-        <v>4907776808.4300003</v>
+        <v>4907776808.43</v>
       </c>
       <c r="H10">
-        <v>3.2231083693563457E-2</v>
+        <v>0.03223108369356346</v>
       </c>
       <c r="I10">
-        <v>-1.270772636690469E-2</v>
+        <v>-0.01270772636690469</v>
       </c>
       <c r="J10">
-        <v>-0.28277843471613068</v>
-      </c>
-      <c r="K10" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>24</v>
+        <v>-0.2827784347161307</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Guaianases</t>
+        </is>
       </c>
       <c r="B11">
-        <v>3.1063500787100792E-2</v>
+        <v>0.03106350078710079</v>
       </c>
       <c r="C11">
-        <v>515288534.05000001</v>
+        <v>515288534.05</v>
       </c>
       <c r="D11">
         <v>686451804.38</v>
       </c>
       <c r="E11">
-        <v>920953728.13999999</v>
+        <v>920953728.14</v>
       </c>
       <c r="F11">
-        <v>1001849833.8200001</v>
+        <v>1001849833.82</v>
       </c>
       <c r="G11">
-        <v>3124543900.3899999</v>
+        <v>3124543900.39</v>
       </c>
       <c r="H11">
-        <v>2.0519970627983719E-2</v>
+        <v>0.02051997062798372</v>
       </c>
       <c r="I11">
-        <v>-1.0543530159117071E-2</v>
+        <v>-0.01054353015911707</v>
       </c>
       <c r="J11">
-        <v>-0.33941860678804431</v>
-      </c>
-      <c r="K11" t="s">
-        <v>17</v>
-      </c>
-      <c r="L11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>25</v>
+        <v>-0.3394186067880443</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ipiranga</t>
+        </is>
       </c>
       <c r="B12">
-        <v>2.8527378000777221E-2</v>
+        <v>0.02852737800077722</v>
       </c>
       <c r="C12">
-        <v>585362030.51999998</v>
+        <v>585362030.52</v>
       </c>
       <c r="D12">
         <v>1081771738.47</v>
       </c>
       <c r="E12">
-        <v>1187638555.1700001</v>
+        <v>1187638555.17</v>
       </c>
       <c r="F12">
-        <v>1586731737.6300001</v>
+        <v>1586731737.63</v>
       </c>
       <c r="G12">
         <v>4441504061.79</v>
       </c>
       <c r="H12">
-        <v>2.9168907782228731E-2</v>
+        <v>0.02916890778222873</v>
       </c>
       <c r="I12">
-        <v>6.4152978145151293E-4</v>
+        <v>0.0006415297814515129</v>
       </c>
       <c r="J12">
-        <v>2.2488214003896001E-2</v>
-      </c>
-      <c r="K12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>26</v>
+        <v>0.022488214003896</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Itaim Paulista</t>
+        </is>
       </c>
       <c r="B13">
-        <v>3.4400609171277553E-2</v>
+        <v>0.03440060917127755</v>
       </c>
       <c r="C13">
-        <v>677606342.20000005</v>
+        <v>677606342.2</v>
       </c>
       <c r="D13">
-        <v>729781207.34000003</v>
+        <v>729781207.34</v>
       </c>
       <c r="E13">
         <v>809483850.37</v>
       </c>
       <c r="F13">
-        <v>1202924802.6099999</v>
+        <v>1202924802.61</v>
       </c>
       <c r="G13">
         <v>3419796202.52</v>
       </c>
       <c r="H13">
-        <v>2.2458995573927332E-2</v>
+        <v>0.02245899557392733</v>
       </c>
       <c r="I13">
-        <v>-1.1941613597350209E-2</v>
+        <v>-0.01194161359735021</v>
       </c>
       <c r="J13">
-        <v>-0.34713378294826103</v>
-      </c>
-      <c r="K13" t="s">
-        <v>17</v>
-      </c>
-      <c r="L13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>27</v>
+        <v>-0.347133782948261</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Itaquera</t>
+        </is>
       </c>
       <c r="B14">
-        <v>4.9820710413288713E-2</v>
+        <v>0.04982071041328871</v>
       </c>
       <c r="C14">
-        <v>892661593.18999994</v>
+        <v>892661593.1899999</v>
       </c>
       <c r="D14">
-        <v>1104357795.9200001</v>
+        <v>1104357795.92</v>
       </c>
       <c r="E14">
-        <v>1381059096.6199999</v>
+        <v>1381059096.62</v>
       </c>
       <c r="F14">
-        <v>2039768606.4100001</v>
+        <v>2039768606.41</v>
       </c>
       <c r="G14">
-        <v>5417847092.1400003</v>
+        <v>5417847092.14</v>
       </c>
       <c r="H14">
-        <v>3.5580893321339881E-2</v>
+        <v>0.03558089332133988</v>
       </c>
       <c r="I14">
-        <v>-1.4239817091948831E-2</v>
+        <v>-0.01423981709194883</v>
       </c>
       <c r="J14">
-        <v>-0.28582123726904213</v>
-      </c>
-      <c r="K14" t="s">
-        <v>14</v>
-      </c>
-      <c r="L14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>28</v>
+        <v>-0.2858212372690421</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Jabaquara</t>
+        </is>
       </c>
       <c r="B15">
-        <v>1.46420577822676E-2</v>
+        <v>0.0146420577822676</v>
       </c>
       <c r="C15">
-        <v>289068585.25999999</v>
+        <v>289068585.26</v>
       </c>
       <c r="D15">
-        <v>1149596326.0599999</v>
+        <v>1149596326.06</v>
       </c>
       <c r="E15">
-        <v>1278748563.5999999</v>
+        <v>1278748563.6</v>
       </c>
       <c r="F15">
-        <v>1532982112.9000001</v>
+        <v>1532982112.9</v>
       </c>
       <c r="G15">
-        <v>4250395587.8200002</v>
+        <v>4250395587.82</v>
       </c>
       <c r="H15">
-        <v>2.7913831714283681E-2</v>
+        <v>0.02791383171428368</v>
       </c>
       <c r="I15">
-        <v>1.3271773932016079E-2</v>
+        <v>0.01327177393201608</v>
       </c>
       <c r="J15">
-        <v>0.90641453061939081</v>
-      </c>
-      <c r="K15" t="s">
-        <v>13</v>
-      </c>
-      <c r="L15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>29</v>
+        <v>0.9064145306193908</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Jaçanã/Tremembé</t>
+        </is>
       </c>
       <c r="B16">
-        <v>3.6195886197592238E-2</v>
+        <v>0.03619588619759224</v>
       </c>
       <c r="C16">
-        <v>418653600.76999998</v>
+        <v>418653600.77</v>
       </c>
       <c r="D16">
-        <v>716643418.79999995</v>
+        <v>716643418.8</v>
       </c>
       <c r="E16">
         <v>1018298108.3</v>
@@ -1120,378 +1054,438 @@
         <v>1078973096.78</v>
       </c>
       <c r="G16">
-        <v>3232568224.6500001</v>
+        <v>3232568224.65</v>
       </c>
       <c r="H16">
-        <v>2.1229404078621519E-2</v>
+        <v>0.02122940407862152</v>
       </c>
       <c r="I16">
-        <v>-1.496648211897071E-2</v>
+        <v>-0.01496648211897071</v>
       </c>
       <c r="J16">
-        <v>-0.41348572147865492</v>
-      </c>
-      <c r="K16" t="s">
-        <v>17</v>
-      </c>
-      <c r="L16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>30</v>
+        <v>-0.4134857214786549</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Lapa</t>
+        </is>
       </c>
       <c r="B17">
-        <v>1.196759457375883E-2</v>
+        <v>0.01196759457375883</v>
       </c>
       <c r="C17">
         <v>439828459.44</v>
       </c>
       <c r="D17">
-        <v>1105161010.5999999</v>
+        <v>1105161010.6</v>
       </c>
       <c r="E17">
         <v>1270053924.95</v>
       </c>
       <c r="F17">
-        <v>1635541987.1300001</v>
+        <v>1635541987.13</v>
       </c>
       <c r="G17">
-        <v>4450585382.1199999</v>
+        <v>4450585382.12</v>
       </c>
       <c r="H17">
-        <v>2.9228547983287081E-2</v>
+        <v>0.02922854798328708</v>
       </c>
       <c r="I17">
-        <v>1.7260953409528251E-2</v>
+        <v>0.01726095340952825</v>
       </c>
       <c r="J17">
-        <v>1.4423076670207471</v>
-      </c>
-      <c r="K17" t="s">
-        <v>13</v>
-      </c>
-      <c r="L17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>31</v>
+        <v>1.442307667020747</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>M'Boi Mirim</t>
+        </is>
       </c>
       <c r="B18">
-        <v>7.6800100060006704E-2</v>
+        <v>0.0768001000600067</v>
       </c>
       <c r="C18">
-        <v>407603040.74000001</v>
+        <v>407603040.74</v>
       </c>
       <c r="D18">
-        <v>1414739277.9000001</v>
+        <v>1414739277.9</v>
       </c>
       <c r="E18">
         <v>1550313121.75</v>
       </c>
       <c r="F18">
-        <v>3036975936.5900002</v>
+        <v>3036975936.59</v>
       </c>
       <c r="G18">
-        <v>6409631376.9799995</v>
+        <v>6409631376.98</v>
       </c>
       <c r="H18">
-        <v>4.2094286969504791E-2</v>
+        <v>0.04209428696950479</v>
       </c>
       <c r="I18">
-        <v>-3.4705813090501907E-2</v>
+        <v>-0.03470581309050191</v>
       </c>
       <c r="J18">
-        <v>-0.45189801918727968</v>
-      </c>
-      <c r="K18" t="s">
-        <v>17</v>
-      </c>
-      <c r="L18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>32</v>
+        <v>-0.4518980191872797</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Mooca</t>
+        </is>
       </c>
       <c r="B19">
-        <v>1.5186931167277059E-2</v>
+        <v>0.01518693116727706</v>
       </c>
       <c r="C19">
-        <v>444011947.81999999</v>
+        <v>444011947.82</v>
       </c>
       <c r="D19">
-        <v>1177863319.1600001</v>
+        <v>1177863319.16</v>
       </c>
       <c r="E19">
-        <v>1879548379.3699999</v>
+        <v>1879548379.37</v>
       </c>
       <c r="F19">
-        <v>2415839399.7800002</v>
+        <v>2415839399.78</v>
       </c>
       <c r="G19">
-        <v>5917263046.1300001</v>
+        <v>5917263046.13</v>
       </c>
       <c r="H19">
-        <v>3.886073224622813E-2</v>
+        <v>0.03886073224622813</v>
       </c>
       <c r="I19">
-        <v>2.3673801078951069E-2</v>
+        <v>0.02367380107895107</v>
       </c>
       <c r="J19">
-        <v>1.5588271796451201</v>
-      </c>
-      <c r="K19" t="s">
-        <v>13</v>
-      </c>
-      <c r="L19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>33</v>
+        <v>1.55882717964512</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Parelheiros</t>
+        </is>
       </c>
       <c r="B20">
-        <v>4.188065349285796E-2</v>
+        <v>0.04188065349285796</v>
       </c>
       <c r="C20">
-        <v>254092379.91999999</v>
+        <v>254092379.92</v>
       </c>
       <c r="D20">
         <v>599141447.25</v>
       </c>
       <c r="E20">
-        <v>891442908.39999998</v>
+        <v>891442908.4</v>
       </c>
       <c r="F20">
-        <v>1294481417.8800001</v>
+        <v>1294481417.88</v>
       </c>
       <c r="G20">
-        <v>3039158153.4499998</v>
+        <v>3039158153.45</v>
       </c>
       <c r="H20">
-        <v>1.9959212618138329E-2</v>
+        <v>0.01995921261813833</v>
       </c>
       <c r="I20">
-        <v>-2.192144087471963E-2</v>
+        <v>-0.02192144087471963</v>
       </c>
       <c r="J20">
-        <v>-0.52342642834973818</v>
-      </c>
-      <c r="K20" t="s">
-        <v>17</v>
-      </c>
-      <c r="L20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>34</v>
+        <v>-0.5234264283497382</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Penha</t>
+        </is>
       </c>
       <c r="B21">
-        <v>3.3286670054792508E-2</v>
+        <v>0.03328667005479251</v>
       </c>
       <c r="C21">
-        <v>413735667.27999997</v>
+        <v>413735667.28</v>
       </c>
       <c r="D21">
         <v>1002662305.98</v>
       </c>
       <c r="E21">
-        <v>1355941790.6800001</v>
+        <v>1355941790.68</v>
       </c>
       <c r="F21">
         <v>1705356170.99</v>
       </c>
       <c r="G21">
-        <v>4477695934.9300003</v>
+        <v>4477695934.93</v>
       </c>
       <c r="H21">
-        <v>2.940659244836891E-2</v>
+        <v>0.02940659244836891</v>
       </c>
       <c r="I21">
-        <v>-3.880077606423601E-3</v>
+        <v>-0.003880077606423601</v>
       </c>
       <c r="J21">
         <v>-0.1165655080558279</v>
       </c>
-      <c r="K21" t="s">
-        <v>14</v>
-      </c>
-      <c r="L21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>35</v>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Perus/Anhanguera</t>
+        </is>
       </c>
       <c r="B22">
-        <v>2.1319194803451E-2</v>
+        <v>0.021319194803451</v>
       </c>
       <c r="C22">
         <v>318856012.44</v>
       </c>
       <c r="D22">
-        <v>378277168.48000002</v>
+        <v>378277168.48</v>
       </c>
       <c r="E22">
         <v>643891246.63</v>
       </c>
       <c r="F22">
-        <v>918890507.58000004</v>
+        <v>918890507.58</v>
       </c>
       <c r="G22">
-        <v>2259914935.1300001</v>
+        <v>2259914935.13</v>
       </c>
       <c r="H22">
-        <v>1.4841650355695461E-2</v>
+        <v>0.01484165035569546</v>
       </c>
       <c r="I22">
-        <v>-6.4775444477555323E-3</v>
+        <v>-0.006477544447755532</v>
       </c>
       <c r="J22">
         <v>-0.3038362615227379</v>
       </c>
-      <c r="K22" t="s">
-        <v>17</v>
-      </c>
-      <c r="L22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>36</v>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Pinheiros</t>
+        </is>
       </c>
       <c r="B23">
-        <v>6.3063713878639006E-3</v>
+        <v>0.006306371387863901</v>
       </c>
       <c r="C23">
-        <v>179126600.34999999</v>
+        <v>179126600.35</v>
       </c>
       <c r="D23">
-        <v>681661685.05999994</v>
+        <v>681661685.0599999</v>
       </c>
       <c r="E23">
-        <v>623666594.00999999</v>
+        <v>623666594.01</v>
       </c>
       <c r="F23">
-        <v>997429393.04999995</v>
+        <v>997429393.05</v>
       </c>
       <c r="G23">
-        <v>2481884272.4699998</v>
+        <v>2481884272.47</v>
       </c>
       <c r="H23">
-        <v>1.6299400487470309E-2</v>
+        <v>0.01629940048747031</v>
       </c>
       <c r="I23">
-        <v>9.9930290996064087E-3</v>
+        <v>0.009993029099606409</v>
       </c>
       <c r="J23">
-        <v>1.5845925469656259</v>
-      </c>
-      <c r="K23" t="s">
-        <v>13</v>
-      </c>
-      <c r="L23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>37</v>
+        <v>1.584592546965626</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Pirituba/Jaraguá</t>
+        </is>
       </c>
       <c r="B24">
-        <v>3.5509983624964131E-2</v>
+        <v>0.03550998362496413</v>
       </c>
       <c r="C24">
-        <v>373444861.42000002</v>
+        <v>373444861.42</v>
       </c>
       <c r="D24">
-        <v>624679391.73000002</v>
+        <v>624679391.73</v>
       </c>
       <c r="E24">
-        <v>856333446.46000004</v>
+        <v>856333446.46</v>
       </c>
       <c r="F24">
-        <v>1785675753.8599999</v>
+        <v>1785675753.86</v>
       </c>
       <c r="G24">
-        <v>3640133453.4699998</v>
+        <v>3640133453.47</v>
       </c>
       <c r="H24">
-        <v>2.3906027224588521E-2</v>
+        <v>0.02390602722458852</v>
       </c>
       <c r="I24">
-        <v>-1.160395640037561E-2</v>
+        <v>-0.01160395640037561</v>
       </c>
       <c r="J24">
-        <v>-0.32678011127602508</v>
-      </c>
-      <c r="K24" t="s">
-        <v>17</v>
-      </c>
-      <c r="L24" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>38</v>
+        <v>-0.3267801112760251</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Santana/Tucuruvi</t>
+        </is>
       </c>
       <c r="B25">
-        <v>1.4423603094699431E-2</v>
+        <v>0.01442360309469943</v>
       </c>
       <c r="C25">
-        <v>166699640.05000001</v>
+        <v>166699640.05</v>
       </c>
       <c r="D25">
-        <v>1743044894.9100001</v>
+        <v>1743044894.91</v>
       </c>
       <c r="E25">
-        <v>1554935421.6700001</v>
+        <v>1554935421.67</v>
       </c>
       <c r="F25">
-        <v>1376552981.1700001</v>
+        <v>1376552981.17</v>
       </c>
       <c r="G25">
-        <v>4841232937.8000002</v>
+        <v>4841232937.8</v>
       </c>
       <c r="H25">
-        <v>3.1794066863481629E-2</v>
+        <v>0.03179406686348163</v>
       </c>
       <c r="I25">
-        <v>1.73704637687822E-2</v>
+        <v>0.0173704637687822</v>
       </c>
       <c r="J25">
         <v>1.204308219987398</v>
       </c>
-      <c r="K25" t="s">
-        <v>13</v>
-      </c>
-      <c r="L25" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>39</v>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Santo Amaro</t>
+        </is>
       </c>
       <c r="B26">
-        <v>7.8084270856710403E-3</v>
+        <v>0.00780842708567104</v>
       </c>
       <c r="C26">
-        <v>214276208.71000001</v>
+        <v>214276208.71</v>
       </c>
       <c r="D26">
-        <v>790575300.34000003</v>
+        <v>790575300.34</v>
       </c>
       <c r="E26">
         <v>849590055.38</v>
@@ -1500,36 +1494,42 @@
         <v>1665436605.22</v>
       </c>
       <c r="G26">
-        <v>3519878169.6500001</v>
+        <v>3519878169.65</v>
       </c>
       <c r="H26">
-        <v>2.3116268792473599E-2</v>
+        <v>0.0231162687924736</v>
       </c>
       <c r="I26">
-        <v>1.530784170680256E-2</v>
+        <v>0.01530784170680256</v>
       </c>
       <c r="J26">
         <v>1.960425773187205</v>
       </c>
-      <c r="K26" t="s">
-        <v>13</v>
-      </c>
-      <c r="L26" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>40</v>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sapopemba</t>
+        </is>
       </c>
       <c r="B27">
-        <v>2.8540780874410629E-2</v>
+        <v>0.02854078087441063</v>
       </c>
       <c r="C27">
-        <v>297798794.47000003</v>
+        <v>297798794.47</v>
       </c>
       <c r="D27">
-        <v>746739859.46000004</v>
+        <v>746739859.46</v>
       </c>
       <c r="E27">
         <v>730973098.37</v>
@@ -1541,147 +1541,171 @@
         <v>2854148107.75</v>
       </c>
       <c r="H27">
-        <v>1.874418705771267E-2</v>
+        <v>0.01874418705771267</v>
       </c>
       <c r="I27">
-        <v>-9.7965938166979551E-3</v>
+        <v>-0.009796593816697955</v>
       </c>
       <c r="J27">
-        <v>-0.34324897625633932</v>
-      </c>
-      <c r="K27" t="s">
-        <v>17</v>
-      </c>
-      <c r="L27" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>41</v>
+        <v>-0.3432489762563393</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>São Mateus</t>
+        </is>
       </c>
       <c r="B28">
-        <v>5.7762104618917447E-2</v>
+        <v>0.05776210461891745</v>
       </c>
       <c r="C28">
-        <v>609449214.60000002</v>
+        <v>609449214.6</v>
       </c>
       <c r="D28">
         <v>1096779160.03</v>
       </c>
       <c r="E28">
-        <v>1424727936.5999999</v>
+        <v>1424727936.6</v>
       </c>
       <c r="F28">
-        <v>1956937590.3800001</v>
+        <v>1956937590.38</v>
       </c>
       <c r="G28">
-        <v>5087893901.6100006</v>
+        <v>5087893901.610001</v>
       </c>
       <c r="H28">
-        <v>3.3413975526573103E-2</v>
+        <v>0.0334139755265731</v>
       </c>
       <c r="I28">
-        <v>-2.4348129092344361E-2</v>
+        <v>-0.02434812909234436</v>
       </c>
       <c r="J28">
-        <v>-0.42152427189036651</v>
-      </c>
-      <c r="K28" t="s">
-        <v>17</v>
-      </c>
-      <c r="L28" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>42</v>
+        <v>-0.4215242718903665</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>São Miguel Paulista</t>
+        </is>
       </c>
       <c r="B29">
-        <v>3.9976751529690907E-2</v>
+        <v>0.03997675152969091</v>
       </c>
       <c r="C29">
-        <v>451987454.60000002</v>
+        <v>451987454.6</v>
       </c>
       <c r="D29">
-        <v>646056157.13999999</v>
+        <v>646056157.14</v>
       </c>
       <c r="E29">
-        <v>757654983.39999998</v>
+        <v>757654983.4</v>
       </c>
       <c r="F29">
         <v>1362970185.21</v>
       </c>
       <c r="G29">
-        <v>3218668780.3499999</v>
+        <v>3218668780.35</v>
       </c>
       <c r="H29">
-        <v>2.1138121575358989E-2</v>
+        <v>0.02113812157535899</v>
       </c>
       <c r="I29">
-        <v>-1.8838629954331929E-2</v>
+        <v>-0.01883862995433193</v>
       </c>
       <c r="J29">
-        <v>-0.47123963887712061</v>
-      </c>
-      <c r="K29" t="s">
-        <v>17</v>
-      </c>
-      <c r="L29" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>43</v>
+        <v>-0.4712396388771206</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Abaixo do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sé</t>
+        </is>
       </c>
       <c r="B30">
-        <v>1.7745398035938359E-2</v>
+        <v>0.01774539803593836</v>
       </c>
       <c r="C30">
         <v>2593261890.04</v>
       </c>
       <c r="D30">
-        <v>4671432106.8000002</v>
+        <v>4671432106.8</v>
       </c>
       <c r="E30">
         <v>11259293445.76</v>
       </c>
       <c r="F30">
-        <v>6837566518.5500002</v>
+        <v>6837566518.55</v>
       </c>
       <c r="G30">
-        <v>25361553961.150002</v>
+        <v>25361553961.15</v>
       </c>
       <c r="H30">
-        <v>0.16655817903466311</v>
+        <v>0.1665581790346631</v>
       </c>
       <c r="I30">
-        <v>0.14881278099872469</v>
+        <v>0.1488127809987247</v>
       </c>
       <c r="J30">
-        <v>8.3859928471227221</v>
-      </c>
-      <c r="K30" t="s">
-        <v>13</v>
-      </c>
-      <c r="L30" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>44</v>
+        <v>8.385992847122722</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Vila Maria/Vila Guilherme</t>
+        </is>
       </c>
       <c r="B31">
-        <v>1.4713894565974181E-2</v>
+        <v>0.01471389456597418</v>
       </c>
       <c r="C31">
-        <v>310244568.83999997</v>
+        <v>310244568.84</v>
       </c>
       <c r="D31">
-        <v>885501416.57000005</v>
+        <v>885501416.5700001</v>
       </c>
       <c r="E31">
         <v>1250274401.01</v>
@@ -1690,98 +1714,114 @@
         <v>1594437761.49</v>
       </c>
       <c r="G31">
-        <v>4040458147.9099998</v>
+        <v>4040458147.91</v>
       </c>
       <c r="H31">
-        <v>2.6535099253482089E-2</v>
+        <v>0.02653509925348209</v>
       </c>
       <c r="I31">
-        <v>1.18212046875079E-2</v>
+        <v>0.0118212046875079</v>
       </c>
       <c r="J31">
-        <v>0.80340419964979126</v>
-      </c>
-      <c r="K31" t="s">
-        <v>13</v>
-      </c>
-      <c r="L31" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>45</v>
+        <v>0.8034041996497913</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Vila Mariana</t>
+        </is>
       </c>
       <c r="B32">
-        <v>7.9495299342696082E-3</v>
+        <v>0.007949529934269608</v>
       </c>
       <c r="C32">
         <v>270403481.87</v>
       </c>
       <c r="D32">
-        <v>918101079.46000004</v>
+        <v>918101079.46</v>
       </c>
       <c r="E32">
-        <v>1373080195.3499999</v>
+        <v>1373080195.35</v>
       </c>
       <c r="F32">
-        <v>1939351672.6600001</v>
+        <v>1939351672.66</v>
       </c>
       <c r="G32">
-        <v>4500936429.3400002</v>
+        <v>4500936429.34</v>
       </c>
       <c r="H32">
-        <v>2.955922088883137E-2</v>
+        <v>0.02955922088883137</v>
       </c>
       <c r="I32">
-        <v>2.160969095456176E-2</v>
+        <v>0.02160969095456176</v>
       </c>
       <c r="J32">
-        <v>2.7183608506717611</v>
-      </c>
-      <c r="K32" t="s">
-        <v>13</v>
-      </c>
-      <c r="L32" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>46</v>
+        <v>2.718360850671761</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Acima do IDRGP Alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Vila Prudente</t>
+        </is>
       </c>
       <c r="B33">
-        <v>1.4705675154435551E-2</v>
+        <v>0.01470567515443555</v>
       </c>
       <c r="C33">
         <v>190978482.88</v>
       </c>
       <c r="D33">
-        <v>490592596.61000001</v>
+        <v>490592596.61</v>
       </c>
       <c r="E33">
-        <v>490806393.49000001</v>
+        <v>490806393.49</v>
       </c>
       <c r="F33">
-        <v>776448481.35000002</v>
+        <v>776448481.35</v>
       </c>
       <c r="G33">
-        <v>1948825954.3299999</v>
+        <v>1948825954.33</v>
       </c>
       <c r="H33">
-        <v>1.279862041205837E-2</v>
+        <v>0.01279862041205837</v>
       </c>
       <c r="I33">
-        <v>-1.907054742377181E-3</v>
+        <v>-0.001907054742377181</v>
       </c>
       <c r="J33">
-        <v>-0.12968154962963199</v>
-      </c>
-      <c r="K33" t="s">
-        <v>14</v>
-      </c>
-      <c r="L33" t="s">
-        <v>14</v>
+        <v>-0.129681549629632</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Dentro do IDRGP Alvo</t>
+        </is>
       </c>
     </row>
   </sheetData>
